--- a/data/nzd0173/nzd0173.xlsx
+++ b/data/nzd0173/nzd0173.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y383"/>
+  <dimension ref="A1:Y384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31481,6 +31481,87 @@
       <c r="Y383" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>381.67</v>
+      </c>
+      <c r="C384" t="n">
+        <v>378.02</v>
+      </c>
+      <c r="D384" t="n">
+        <v>379.18</v>
+      </c>
+      <c r="E384" t="n">
+        <v>373.51</v>
+      </c>
+      <c r="F384" t="n">
+        <v>376.4</v>
+      </c>
+      <c r="G384" t="n">
+        <v>378.57</v>
+      </c>
+      <c r="H384" t="n">
+        <v>383.27</v>
+      </c>
+      <c r="I384" t="n">
+        <v>385.15</v>
+      </c>
+      <c r="J384" t="n">
+        <v>381.83</v>
+      </c>
+      <c r="K384" t="n">
+        <v>377.24</v>
+      </c>
+      <c r="L384" t="n">
+        <v>377.55</v>
+      </c>
+      <c r="M384" t="n">
+        <v>382.09</v>
+      </c>
+      <c r="N384" t="n">
+        <v>385.69</v>
+      </c>
+      <c r="O384" t="n">
+        <v>386.07</v>
+      </c>
+      <c r="P384" t="n">
+        <v>385.95</v>
+      </c>
+      <c r="Q384" t="n">
+        <v>386.27</v>
+      </c>
+      <c r="R384" t="n">
+        <v>385.37</v>
+      </c>
+      <c r="S384" t="n">
+        <v>384.16</v>
+      </c>
+      <c r="T384" t="n">
+        <v>383.17</v>
+      </c>
+      <c r="U384" t="n">
+        <v>382.3</v>
+      </c>
+      <c r="V384" t="n">
+        <v>382.17</v>
+      </c>
+      <c r="W384" t="n">
+        <v>378</v>
+      </c>
+      <c r="X384" t="n">
+        <v>380.3</v>
+      </c>
+      <c r="Y384" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -31495,7 +31576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B461"/>
+  <dimension ref="A1:B462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36108,6 +36189,16 @@
       </c>
       <c r="B461" t="n">
         <v>0.65</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>-0.73</v>
       </c>
     </row>
   </sheetData>
@@ -36276,28 +36367,28 @@
         <v>0.078</v>
       </c>
       <c r="I2" t="n">
-        <v>0.122096926506487</v>
+        <v>0.1205844212273273</v>
       </c>
       <c r="J2" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K2" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03703928643241072</v>
+        <v>0.03630683659858958</v>
       </c>
       <c r="M2" t="n">
-        <v>3.465203670357074</v>
+        <v>3.463451782808546</v>
       </c>
       <c r="N2" t="n">
-        <v>21.68880988227051</v>
+        <v>21.65599080658529</v>
       </c>
       <c r="O2" t="n">
-        <v>4.657124636755013</v>
+        <v>4.653599768629151</v>
       </c>
       <c r="P2" t="n">
-        <v>381.4918720604568</v>
+        <v>381.5076988873533</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -36358,28 +36449,28 @@
         <v>0.0623</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04377928734389964</v>
+        <v>0.04229028237996228</v>
       </c>
       <c r="J3" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K3" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005087311529863414</v>
+        <v>0.004768685972114328</v>
       </c>
       <c r="M3" t="n">
-        <v>3.321526038160538</v>
+        <v>3.320254890336493</v>
       </c>
       <c r="N3" t="n">
-        <v>20.88349529076384</v>
+        <v>20.85218149094207</v>
       </c>
       <c r="O3" t="n">
-        <v>4.569846309315428</v>
+        <v>4.566418891313199</v>
       </c>
       <c r="P3" t="n">
-        <v>379.8630147164178</v>
+        <v>379.8786179982064</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -36440,28 +36531,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02366652904375155</v>
+        <v>0.02198927985438853</v>
       </c>
       <c r="J4" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K4" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001689855866554124</v>
+        <v>0.001464592111299012</v>
       </c>
       <c r="M4" t="n">
-        <v>3.096997042609063</v>
+        <v>3.097415779237152</v>
       </c>
       <c r="N4" t="n">
-        <v>18.43546661446799</v>
+        <v>18.41678465919001</v>
       </c>
       <c r="O4" t="n">
-        <v>4.29365422623527</v>
+        <v>4.291478143855566</v>
       </c>
       <c r="P4" t="n">
-        <v>381.9228567849147</v>
+        <v>381.9404326777863</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -36522,28 +36613,28 @@
         <v>0.0529</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1376621153105724</v>
+        <v>0.1356533935740675</v>
       </c>
       <c r="J5" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K5" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0439121776168846</v>
+        <v>0.04283684169395752</v>
       </c>
       <c r="M5" t="n">
-        <v>3.652901325868224</v>
+        <v>3.652258605041049</v>
       </c>
       <c r="N5" t="n">
-        <v>22.98851227619323</v>
+        <v>22.97073408614182</v>
       </c>
       <c r="O5" t="n">
-        <v>4.794633695726216</v>
+        <v>4.792779369649913</v>
       </c>
       <c r="P5" t="n">
-        <v>373.9140788588018</v>
+        <v>373.9351282522215</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -36604,28 +36695,28 @@
         <v>0.0608</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1473601381235183</v>
+        <v>0.1460287659713869</v>
       </c>
       <c r="J6" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K6" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05679749273362578</v>
+        <v>0.05606506244279819</v>
       </c>
       <c r="M6" t="n">
-        <v>3.242672561095864</v>
+        <v>3.240266524141973</v>
       </c>
       <c r="N6" t="n">
-        <v>20.0911593709896</v>
+        <v>20.05725976254204</v>
       </c>
       <c r="O6" t="n">
-        <v>4.482316295286355</v>
+        <v>4.478533215522917</v>
       </c>
       <c r="P6" t="n">
-        <v>375.1875789861988</v>
+        <v>375.2015304338826</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -36686,28 +36777,28 @@
         <v>0.0674</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1176447294967617</v>
+        <v>0.1168858827008715</v>
       </c>
       <c r="J7" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K7" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0377971999478659</v>
+        <v>0.03750990740045679</v>
       </c>
       <c r="M7" t="n">
-        <v>3.118816176795774</v>
+        <v>3.11407493201958</v>
       </c>
       <c r="N7" t="n">
-        <v>19.63003690939961</v>
+        <v>19.58481239333388</v>
       </c>
       <c r="O7" t="n">
-        <v>4.430579748678452</v>
+        <v>4.425473126495502</v>
       </c>
       <c r="P7" t="n">
-        <v>376.9901900403522</v>
+        <v>376.9981419953003</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -36768,28 +36859,28 @@
         <v>0.0718</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1452850821521193</v>
+        <v>0.1446434306966105</v>
       </c>
       <c r="J8" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K8" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05381295882216786</v>
+        <v>0.05362286195612564</v>
       </c>
       <c r="M8" t="n">
-        <v>3.268779957801689</v>
+        <v>3.26284718488217</v>
       </c>
       <c r="N8" t="n">
-        <v>20.67765797814591</v>
+        <v>20.62797978083284</v>
       </c>
       <c r="O8" t="n">
-        <v>4.547269288061343</v>
+        <v>4.541803582370426</v>
       </c>
       <c r="P8" t="n">
-        <v>380.7246756592711</v>
+        <v>380.7313995243441</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -36850,28 +36941,28 @@
         <v>0.0609</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07982210974174249</v>
+        <v>0.07832624082312239</v>
       </c>
       <c r="J9" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K9" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01802130692044146</v>
+        <v>0.01743405092403516</v>
       </c>
       <c r="M9" t="n">
-        <v>3.108421629334185</v>
+        <v>3.108113696308477</v>
       </c>
       <c r="N9" t="n">
-        <v>19.34333542456845</v>
+        <v>19.3162574293542</v>
       </c>
       <c r="O9" t="n">
-        <v>4.39810589055885</v>
+        <v>4.395026442395336</v>
       </c>
       <c r="P9" t="n">
-        <v>386.0503296066955</v>
+        <v>386.0660048158597</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -36932,28 +37023,28 @@
         <v>0.1019</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0917987028552484</v>
+        <v>0.09044919007832945</v>
       </c>
       <c r="J10" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K10" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02323161476066304</v>
+        <v>0.02266513701072381</v>
       </c>
       <c r="M10" t="n">
-        <v>3.202719420812774</v>
+        <v>3.201416611790782</v>
       </c>
       <c r="N10" t="n">
-        <v>19.74033248049293</v>
+        <v>19.7078580314626</v>
       </c>
       <c r="O10" t="n">
-        <v>4.443009394598771</v>
+        <v>4.439353334829589</v>
       </c>
       <c r="P10" t="n">
-        <v>382.1222585943339</v>
+        <v>382.1364001376099</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -37014,28 +37105,28 @@
         <v>0.0895</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1470950453585906</v>
+        <v>0.145338598120038</v>
       </c>
       <c r="J11" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K11" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05296817885308591</v>
+        <v>0.05196374822279781</v>
       </c>
       <c r="M11" t="n">
-        <v>3.262470422461235</v>
+        <v>3.261531071934969</v>
       </c>
       <c r="N11" t="n">
-        <v>21.55335075397734</v>
+        <v>21.52937520574397</v>
       </c>
       <c r="O11" t="n">
-        <v>4.642558643030515</v>
+        <v>4.639975776417801</v>
       </c>
       <c r="P11" t="n">
-        <v>376.888146917436</v>
+        <v>376.9065527265997</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -37096,28 +37187,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1689894223826606</v>
+        <v>0.1664283407900585</v>
       </c>
       <c r="J12" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K12" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L12" t="n">
-        <v>0.09007720843973621</v>
+        <v>0.08768872070623146</v>
       </c>
       <c r="M12" t="n">
-        <v>2.882710192413378</v>
+        <v>2.886482821898943</v>
       </c>
       <c r="N12" t="n">
-        <v>16.0722931317675</v>
+        <v>16.09899980853064</v>
       </c>
       <c r="O12" t="n">
-        <v>4.009026456855517</v>
+        <v>4.012355892556223</v>
       </c>
       <c r="P12" t="n">
-        <v>378.246419448297</v>
+        <v>378.2732570201929</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -37178,28 +37269,28 @@
         <v>0.0849</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2422500666417963</v>
+        <v>0.2397879425307287</v>
       </c>
       <c r="J13" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K13" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1731712523781698</v>
+        <v>0.1704426057673551</v>
       </c>
       <c r="M13" t="n">
-        <v>2.802903613066491</v>
+        <v>2.806598987598985</v>
       </c>
       <c r="N13" t="n">
-        <v>15.61121689015743</v>
+        <v>15.63392320388381</v>
       </c>
       <c r="O13" t="n">
-        <v>3.95110324974651</v>
+        <v>3.953975620041657</v>
       </c>
       <c r="P13" t="n">
-        <v>380.6525189836928</v>
+        <v>380.6783195802214</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -37260,28 +37351,28 @@
         <v>0.0725</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2201622100022782</v>
+        <v>0.2165566290033533</v>
       </c>
       <c r="J14" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K14" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1258656409943423</v>
+        <v>0.1220700426243136</v>
       </c>
       <c r="M14" t="n">
-        <v>3.170408997700706</v>
+        <v>3.179679159216297</v>
       </c>
       <c r="N14" t="n">
-        <v>18.75537397478391</v>
+        <v>18.84251004152834</v>
       </c>
       <c r="O14" t="n">
-        <v>4.330747507623125</v>
+        <v>4.340796014733741</v>
       </c>
       <c r="P14" t="n">
-        <v>387.1338198465727</v>
+        <v>387.1716027268859</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -37342,28 +37433,28 @@
         <v>0.0575</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2210650130055937</v>
+        <v>0.2164129201504217</v>
       </c>
       <c r="J15" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K15" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1337193609052361</v>
+        <v>0.1280314085746973</v>
       </c>
       <c r="M15" t="n">
-        <v>3.031432620179413</v>
+        <v>3.047696151451183</v>
       </c>
       <c r="N15" t="n">
-        <v>17.63898216701854</v>
+        <v>17.81950791255888</v>
       </c>
       <c r="O15" t="n">
-        <v>4.199878827659025</v>
+        <v>4.221315898219284</v>
       </c>
       <c r="P15" t="n">
-        <v>389.5899348013041</v>
+        <v>389.6386840784957</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -37424,28 +37515,28 @@
         <v>0.0631</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2330898405575005</v>
+        <v>0.2291960302109766</v>
       </c>
       <c r="J16" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K16" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1346793233848869</v>
+        <v>0.1304796855921887</v>
       </c>
       <c r="M16" t="n">
-        <v>3.174416479411486</v>
+        <v>3.186465015844877</v>
       </c>
       <c r="N16" t="n">
-        <v>19.44876468960714</v>
+        <v>19.55672062330999</v>
       </c>
       <c r="O16" t="n">
-        <v>4.410075360989553</v>
+        <v>4.422298115607991</v>
       </c>
       <c r="P16" t="n">
-        <v>387.6283660747249</v>
+        <v>387.6691693101338</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -37506,28 +37597,28 @@
         <v>0.068</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1912619936910541</v>
+        <v>0.1878560018467643</v>
       </c>
       <c r="J17" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K17" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1022904318634851</v>
+        <v>0.09890681980351679</v>
       </c>
       <c r="M17" t="n">
-        <v>2.983839343406177</v>
+        <v>2.994839900664774</v>
       </c>
       <c r="N17" t="n">
-        <v>17.88658273901533</v>
+        <v>17.96133582050103</v>
       </c>
       <c r="O17" t="n">
-        <v>4.229253212922505</v>
+        <v>4.238081620320806</v>
       </c>
       <c r="P17" t="n">
-        <v>388.0776898798405</v>
+        <v>388.1133812655669</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -37588,28 +37679,28 @@
         <v>0.0687</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1958818882022949</v>
+        <v>0.192174009265777</v>
       </c>
       <c r="J18" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K18" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0939297034365254</v>
+        <v>0.09059071232056259</v>
       </c>
       <c r="M18" t="n">
-        <v>3.267794587811998</v>
+        <v>3.277242841347017</v>
       </c>
       <c r="N18" t="n">
-        <v>20.62133048927667</v>
+        <v>20.71142738101273</v>
       </c>
       <c r="O18" t="n">
-        <v>4.541071513340951</v>
+        <v>4.550980925142702</v>
       </c>
       <c r="P18" t="n">
-        <v>387.6567769686424</v>
+        <v>387.6956318289593</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -37670,28 +37761,28 @@
         <v>0.0696</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2398454914636106</v>
+        <v>0.2350898124372434</v>
       </c>
       <c r="J19" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K19" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1110956981593232</v>
+        <v>0.1068293140505933</v>
       </c>
       <c r="M19" t="n">
-        <v>3.917547249685292</v>
+        <v>3.929893384102773</v>
       </c>
       <c r="N19" t="n">
-        <v>25.64425345898124</v>
+        <v>25.81408039597725</v>
       </c>
       <c r="O19" t="n">
-        <v>5.064015546873967</v>
+        <v>5.080755888249035</v>
       </c>
       <c r="P19" t="n">
-        <v>387.4009263571377</v>
+        <v>387.4507611137317</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -37752,28 +37843,28 @@
         <v>0.0623</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2771119623177481</v>
+        <v>0.2712387499423937</v>
       </c>
       <c r="J20" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K20" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1356693734069864</v>
+        <v>0.1298310083255424</v>
       </c>
       <c r="M20" t="n">
-        <v>3.880492755283708</v>
+        <v>3.902220882228646</v>
       </c>
       <c r="N20" t="n">
-        <v>27.25698449898368</v>
+        <v>27.54695881338682</v>
       </c>
       <c r="O20" t="n">
-        <v>5.220822205264577</v>
+        <v>5.248519678288995</v>
       </c>
       <c r="P20" t="n">
-        <v>387.6708784470962</v>
+        <v>387.7324238347323</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -37834,28 +37925,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1071043490576142</v>
+        <v>0.1015416372074639</v>
       </c>
       <c r="J21" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K21" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02298167343857949</v>
+        <v>0.02057196908497771</v>
       </c>
       <c r="M21" t="n">
-        <v>3.930705649213215</v>
+        <v>3.948603448719903</v>
       </c>
       <c r="N21" t="n">
-        <v>27.17092664641434</v>
+        <v>27.42394993003443</v>
       </c>
       <c r="O21" t="n">
-        <v>5.212573898412793</v>
+        <v>5.236788131100439</v>
       </c>
       <c r="P21" t="n">
-        <v>390.6549108084386</v>
+        <v>390.7132024613272</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -37916,28 +38007,28 @@
         <v>0.0607</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1745125791960664</v>
+        <v>0.1680779818265092</v>
       </c>
       <c r="J22" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K22" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0495986866077649</v>
+        <v>0.04582341317083249</v>
       </c>
       <c r="M22" t="n">
-        <v>4.257074355409524</v>
+        <v>4.277787072670095</v>
       </c>
       <c r="N22" t="n">
-        <v>32.65657438959926</v>
+        <v>33.00716735325983</v>
       </c>
       <c r="O22" t="n">
-        <v>5.71459310796484</v>
+        <v>5.745186450695907</v>
       </c>
       <c r="P22" t="n">
-        <v>390.516774123611</v>
+        <v>390.5841056299005</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -37998,28 +38089,28 @@
         <v>0.0672</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2018429119232842</v>
+        <v>0.1933308973608308</v>
       </c>
       <c r="J23" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K23" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L23" t="n">
-        <v>0.04928239903651155</v>
+        <v>0.04488327642975631</v>
       </c>
       <c r="M23" t="n">
-        <v>5.02575577765958</v>
+        <v>5.0513738485386</v>
       </c>
       <c r="N23" t="n">
-        <v>43.98119240690306</v>
+        <v>44.62926299963841</v>
       </c>
       <c r="O23" t="n">
-        <v>6.631831753512981</v>
+        <v>6.680513677827358</v>
       </c>
       <c r="P23" t="n">
-        <v>389.7977156426073</v>
+        <v>389.8867852034721</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -38080,28 +38171,28 @@
         <v>0.0461</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2122835511533846</v>
+        <v>0.203314851231379</v>
       </c>
       <c r="J24" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K24" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0525378352096636</v>
+        <v>0.04779806962008637</v>
       </c>
       <c r="M24" t="n">
-        <v>5.120787447203382</v>
+        <v>5.144752701582578</v>
       </c>
       <c r="N24" t="n">
-        <v>45.47813962251141</v>
+        <v>46.20640610003759</v>
       </c>
       <c r="O24" t="n">
-        <v>6.743748187952409</v>
+        <v>6.797529411487499</v>
       </c>
       <c r="P24" t="n">
-        <v>392.7450938618524</v>
+        <v>392.8389421697612</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -38143,7 +38234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y383"/>
+  <dimension ref="A1:Y384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86755,6 +86846,133 @@
         </is>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>-36.78510408744357,175.0668884480548</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>-36.78533009543281,175.067742907781</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>-36.78551421289902,175.0686112018258</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>-36.78575766774659,175.06945906731053</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>-36.78591919965647,175.07033356988728</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>-36.786086006076765,175.0712068678706</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>-36.78622832257008,175.07208729374383</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>-36.786389863000316,175.07294494651455</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>-36.78651541607623,175.07381000998132</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>-36.786639190717885,175.0746999635173</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>-36.786758948117686,175.07559226260074</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>-36.786850770937434,175.07648536021176</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>-36.78695008359549,175.077368993367</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>-36.78704638012752,175.0782437308056</t>
+        </is>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>-36.78710971567916,175.0791306475438</t>
+        </is>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>-36.787169491768424,175.08002580644705</t>
+        </is>
+      </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t>-36.787240174246115,175.08091836037102</t>
+        </is>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>-36.78730560657817,175.08181108775565</t>
+        </is>
+      </c>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>-36.78736635397724,175.08270589221448</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>-36.78742603508954,175.08360130037758</t>
+        </is>
+      </c>
+      <c r="V384" t="inlineStr">
+        <is>
+          <t>-36.78747908631666,175.0844983041342</t>
+        </is>
+      </c>
+      <c r="W384" t="inlineStr">
+        <is>
+          <t>-36.78757503005989,175.08539712933313</t>
+        </is>
+      </c>
+      <c r="X384" t="inlineStr">
+        <is>
+          <t>-36.78765293395494,175.08629588079984</t>
+        </is>
+      </c>
+      <c r="Y384" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0173/nzd0173.xlsx
+++ b/data/nzd0173/nzd0173.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y384"/>
+  <dimension ref="A1:Y385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31562,6 +31562,87 @@
       <c r="Y384" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>380.22</v>
+      </c>
+      <c r="C385" t="n">
+        <v>377.76</v>
+      </c>
+      <c r="D385" t="n">
+        <v>379.42</v>
+      </c>
+      <c r="E385" t="n">
+        <v>373.55</v>
+      </c>
+      <c r="F385" t="n">
+        <v>376.69</v>
+      </c>
+      <c r="G385" t="n">
+        <v>378.96</v>
+      </c>
+      <c r="H385" t="n">
+        <v>383.62</v>
+      </c>
+      <c r="I385" t="n">
+        <v>386.02</v>
+      </c>
+      <c r="J385" t="n">
+        <v>382.5</v>
+      </c>
+      <c r="K385" t="n">
+        <v>377.49</v>
+      </c>
+      <c r="L385" t="n">
+        <v>378.43</v>
+      </c>
+      <c r="M385" t="n">
+        <v>382.51</v>
+      </c>
+      <c r="N385" t="n">
+        <v>386.07</v>
+      </c>
+      <c r="O385" t="n">
+        <v>386.98</v>
+      </c>
+      <c r="P385" t="n">
+        <v>386.2</v>
+      </c>
+      <c r="Q385" t="n">
+        <v>386.12</v>
+      </c>
+      <c r="R385" t="n">
+        <v>384.34</v>
+      </c>
+      <c r="S385" t="n">
+        <v>383.64</v>
+      </c>
+      <c r="T385" t="n">
+        <v>382.81</v>
+      </c>
+      <c r="U385" t="n">
+        <v>382.21</v>
+      </c>
+      <c r="V385" t="n">
+        <v>381.66</v>
+      </c>
+      <c r="W385" t="n">
+        <v>376.48</v>
+      </c>
+      <c r="X385" t="n">
+        <v>379.3</v>
+      </c>
+      <c r="Y385" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -31576,7 +31657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B462"/>
+  <dimension ref="A1:B463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36199,6 +36280,16 @@
       </c>
       <c r="B462" t="n">
         <v>-0.73</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>
@@ -36367,28 +36458,28 @@
         <v>0.078</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1205844212273273</v>
+        <v>0.1183761974341612</v>
       </c>
       <c r="J2" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K2" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03630683659858958</v>
+        <v>0.03513287715939339</v>
       </c>
       <c r="M2" t="n">
-        <v>3.463451782808546</v>
+        <v>3.465053795955396</v>
       </c>
       <c r="N2" t="n">
-        <v>21.65599080658529</v>
+        <v>21.65115409677992</v>
       </c>
       <c r="O2" t="n">
-        <v>4.653599768629151</v>
+        <v>4.653080065588805</v>
       </c>
       <c r="P2" t="n">
-        <v>381.5076988873533</v>
+        <v>381.5308296811315</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -36449,28 +36540,28 @@
         <v>0.0623</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04229028237996228</v>
+        <v>0.04069311185287491</v>
       </c>
       <c r="J3" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K3" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004768685972114328</v>
+        <v>0.004434444562375295</v>
       </c>
       <c r="M3" t="n">
-        <v>3.320254890336493</v>
+        <v>3.319552283617357</v>
       </c>
       <c r="N3" t="n">
-        <v>20.85218149094207</v>
+        <v>20.82483061520171</v>
       </c>
       <c r="O3" t="n">
-        <v>4.566418891313199</v>
+        <v>4.563423124716982</v>
       </c>
       <c r="P3" t="n">
-        <v>379.8786179982064</v>
+        <v>379.8953719650088</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -36531,28 +36622,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02198927985438853</v>
+        <v>0.02045836786539109</v>
       </c>
       <c r="J4" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K4" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001464592111299012</v>
+        <v>0.001273008734774428</v>
       </c>
       <c r="M4" t="n">
-        <v>3.097415779237152</v>
+        <v>3.097108199998415</v>
       </c>
       <c r="N4" t="n">
-        <v>18.41678465919001</v>
+        <v>18.39358616840078</v>
       </c>
       <c r="O4" t="n">
-        <v>4.291478143855566</v>
+        <v>4.288774436642801</v>
       </c>
       <c r="P4" t="n">
-        <v>381.9404326777863</v>
+        <v>381.956491607128</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -36613,28 +36704,28 @@
         <v>0.0529</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1356533935740675</v>
+        <v>0.1336919485646245</v>
       </c>
       <c r="J5" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K5" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04283684169395752</v>
+        <v>0.04179881788546047</v>
       </c>
       <c r="M5" t="n">
-        <v>3.652258605041049</v>
+        <v>3.651437957666344</v>
       </c>
       <c r="N5" t="n">
-        <v>22.97073408614182</v>
+        <v>22.95156212563739</v>
       </c>
       <c r="O5" t="n">
-        <v>4.792779369649913</v>
+        <v>4.790778864197073</v>
       </c>
       <c r="P5" t="n">
-        <v>373.9351282522215</v>
+        <v>373.9557033780554</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -36695,28 +36786,28 @@
         <v>0.0608</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1460287659713869</v>
+        <v>0.1448594140704455</v>
       </c>
       <c r="J6" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K6" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05606506244279819</v>
+        <v>0.05545883144474018</v>
       </c>
       <c r="M6" t="n">
-        <v>3.240266524141973</v>
+        <v>3.237139771062067</v>
       </c>
       <c r="N6" t="n">
-        <v>20.05725976254204</v>
+        <v>20.01947418382836</v>
       </c>
       <c r="O6" t="n">
-        <v>4.478533215522917</v>
+        <v>4.474312705190414</v>
       </c>
       <c r="P6" t="n">
-        <v>375.2015304338826</v>
+        <v>375.2137966775907</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -36777,28 +36868,28 @@
         <v>0.0674</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1168858827008715</v>
+        <v>0.1163309902817009</v>
       </c>
       <c r="J7" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K7" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03750990740045679</v>
+        <v>0.03735152451401669</v>
       </c>
       <c r="M7" t="n">
-        <v>3.11407493201958</v>
+        <v>3.108454201689568</v>
       </c>
       <c r="N7" t="n">
-        <v>19.58481239333388</v>
+        <v>19.53706340349256</v>
       </c>
       <c r="O7" t="n">
-        <v>4.425473126495502</v>
+        <v>4.420075045006879</v>
       </c>
       <c r="P7" t="n">
-        <v>376.9981419953003</v>
+        <v>377.0039626944755</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -36859,28 +36950,28 @@
         <v>0.0718</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1446434306966105</v>
+        <v>0.1441830600104624</v>
       </c>
       <c r="J8" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K8" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05362286195612564</v>
+        <v>0.05356216227897681</v>
       </c>
       <c r="M8" t="n">
-        <v>3.26284718488217</v>
+        <v>3.256230095653232</v>
       </c>
       <c r="N8" t="n">
-        <v>20.62797978083284</v>
+        <v>20.57650031292535</v>
       </c>
       <c r="O8" t="n">
-        <v>4.541803582370426</v>
+        <v>4.536132748600436</v>
       </c>
       <c r="P8" t="n">
-        <v>380.7313995243441</v>
+        <v>380.736228711373</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -36941,28 +37032,28 @@
         <v>0.0609</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07832624082312239</v>
+        <v>0.07728071036885986</v>
       </c>
       <c r="J9" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K9" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01743405092403516</v>
+        <v>0.01705800895865472</v>
       </c>
       <c r="M9" t="n">
-        <v>3.108113696308477</v>
+        <v>3.105569280514577</v>
       </c>
       <c r="N9" t="n">
-        <v>19.3162574293542</v>
+        <v>19.27750400176511</v>
       </c>
       <c r="O9" t="n">
-        <v>4.395026442395336</v>
+        <v>4.390615446809832</v>
       </c>
       <c r="P9" t="n">
-        <v>386.0660048158597</v>
+        <v>386.0769721998831</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -37023,28 +37114,28 @@
         <v>0.1019</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09044919007832945</v>
+        <v>0.08944897938466813</v>
       </c>
       <c r="J10" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K10" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02266513701072381</v>
+        <v>0.02228093748939608</v>
       </c>
       <c r="M10" t="n">
-        <v>3.201416611790782</v>
+        <v>3.198287680636208</v>
       </c>
       <c r="N10" t="n">
-        <v>19.7078580314626</v>
+        <v>19.66710527203128</v>
       </c>
       <c r="O10" t="n">
-        <v>4.439353334829589</v>
+        <v>4.434761016338004</v>
       </c>
       <c r="P10" t="n">
-        <v>382.1364001376099</v>
+        <v>382.1468921273334</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -37105,28 +37196,28 @@
         <v>0.0895</v>
       </c>
       <c r="I11" t="n">
-        <v>0.145338598120038</v>
+        <v>0.1437307081570878</v>
       </c>
       <c r="J11" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K11" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05196374822279781</v>
+        <v>0.05107283777400462</v>
       </c>
       <c r="M11" t="n">
-        <v>3.261531071934969</v>
+        <v>3.260033695511018</v>
       </c>
       <c r="N11" t="n">
-        <v>21.52937520574397</v>
+        <v>21.50062379200502</v>
       </c>
       <c r="O11" t="n">
-        <v>4.639975776417801</v>
+        <v>4.636876512481761</v>
       </c>
       <c r="P11" t="n">
-        <v>376.9065527265997</v>
+        <v>376.9234191379217</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -37187,28 +37278,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1664283407900585</v>
+        <v>0.1643322059334036</v>
       </c>
       <c r="J12" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K12" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L12" t="n">
-        <v>0.08768872070623146</v>
+        <v>0.08587012841122199</v>
       </c>
       <c r="M12" t="n">
-        <v>2.886482821898943</v>
+        <v>2.888300437939812</v>
       </c>
       <c r="N12" t="n">
-        <v>16.09899980853064</v>
+        <v>16.10349710142492</v>
       </c>
       <c r="O12" t="n">
-        <v>4.012355892556223</v>
+        <v>4.012916283879458</v>
       </c>
       <c r="P12" t="n">
-        <v>378.2732570201929</v>
+        <v>378.2952450128375</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -37269,28 +37360,28 @@
         <v>0.0849</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2397879425307287</v>
+        <v>0.2375665800804572</v>
       </c>
       <c r="J13" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K13" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1704426057673551</v>
+        <v>0.1680993646381777</v>
       </c>
       <c r="M13" t="n">
-        <v>2.806598987598985</v>
+        <v>2.809347815550699</v>
       </c>
       <c r="N13" t="n">
-        <v>15.63392320388381</v>
+        <v>15.64534399128915</v>
       </c>
       <c r="O13" t="n">
-        <v>3.953975620041657</v>
+        <v>3.955419572092087</v>
       </c>
       <c r="P13" t="n">
-        <v>380.6783195802214</v>
+        <v>380.701621182722</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -37351,28 +37442,28 @@
         <v>0.0725</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2165566290033533</v>
+        <v>0.2131854521563736</v>
       </c>
       <c r="J14" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K14" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1220700426243136</v>
+        <v>0.1186337732543218</v>
       </c>
       <c r="M14" t="n">
-        <v>3.179679159216297</v>
+        <v>3.188202836486211</v>
       </c>
       <c r="N14" t="n">
-        <v>18.84251004152834</v>
+        <v>18.91351427587775</v>
       </c>
       <c r="O14" t="n">
-        <v>4.340796014733741</v>
+        <v>4.34896703550139</v>
       </c>
       <c r="P14" t="n">
-        <v>387.1716027268859</v>
+        <v>387.2069656289814</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -37433,28 +37524,28 @@
         <v>0.0575</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2164129201504217</v>
+        <v>0.212273620944569</v>
       </c>
       <c r="J15" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K15" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1280314085746973</v>
+        <v>0.1232563808950256</v>
       </c>
       <c r="M15" t="n">
-        <v>3.047696151451183</v>
+        <v>3.061949718672672</v>
       </c>
       <c r="N15" t="n">
-        <v>17.81950791255888</v>
+        <v>17.95412725812401</v>
       </c>
       <c r="O15" t="n">
-        <v>4.221315898219284</v>
+        <v>4.237231083871166</v>
       </c>
       <c r="P15" t="n">
-        <v>389.6386840784957</v>
+        <v>389.6821044148364</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -37515,28 +37606,28 @@
         <v>0.0631</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2291960302109766</v>
+        <v>0.2254791107759251</v>
       </c>
       <c r="J16" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K16" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1304796855921887</v>
+        <v>0.1265744822235193</v>
       </c>
       <c r="M16" t="n">
-        <v>3.186465015844877</v>
+        <v>3.197943918040105</v>
       </c>
       <c r="N16" t="n">
-        <v>19.55672062330999</v>
+        <v>19.6517569437334</v>
       </c>
       <c r="O16" t="n">
-        <v>4.422298115607991</v>
+        <v>4.433030221387329</v>
       </c>
       <c r="P16" t="n">
-        <v>387.6691693101338</v>
+        <v>387.7081589757742</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -37597,28 +37688,28 @@
         <v>0.068</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1878560018467643</v>
+        <v>0.1844174295706193</v>
       </c>
       <c r="J17" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K17" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09890681980351679</v>
+        <v>0.09551871100626186</v>
       </c>
       <c r="M17" t="n">
-        <v>2.994839900664774</v>
+        <v>3.00609832524362</v>
       </c>
       <c r="N17" t="n">
-        <v>17.96133582050103</v>
+        <v>18.0394836972288</v>
       </c>
       <c r="O17" t="n">
-        <v>4.238081620320806</v>
+        <v>4.247291336514226</v>
       </c>
       <c r="P17" t="n">
-        <v>388.1133812655669</v>
+        <v>388.14945113086</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -37679,28 +37770,28 @@
         <v>0.0687</v>
       </c>
       <c r="I18" t="n">
-        <v>0.192174009265777</v>
+        <v>0.1880079009683958</v>
       </c>
       <c r="J18" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K18" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L18" t="n">
-        <v>0.09059071232056259</v>
+        <v>0.08676197361825611</v>
       </c>
       <c r="M18" t="n">
-        <v>3.277242841347017</v>
+        <v>3.289820746324281</v>
       </c>
       <c r="N18" t="n">
-        <v>20.71142738101273</v>
+        <v>20.84086816831965</v>
       </c>
       <c r="O18" t="n">
-        <v>4.550980925142702</v>
+        <v>4.565179971076677</v>
       </c>
       <c r="P18" t="n">
-        <v>387.6956318289593</v>
+        <v>387.7393333867614</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -37761,28 +37852,28 @@
         <v>0.0696</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2350898124372434</v>
+        <v>0.2301350532653222</v>
       </c>
       <c r="J19" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K19" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1068293140505933</v>
+        <v>0.1023957785378607</v>
       </c>
       <c r="M19" t="n">
-        <v>3.929893384102773</v>
+        <v>3.943281436387589</v>
       </c>
       <c r="N19" t="n">
-        <v>25.81408039597725</v>
+        <v>26.00623138162942</v>
       </c>
       <c r="O19" t="n">
-        <v>5.080755888249035</v>
+        <v>5.09963051422644</v>
       </c>
       <c r="P19" t="n">
-        <v>387.4507611137317</v>
+        <v>387.5027354453839</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -37843,28 +37934,28 @@
         <v>0.0623</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2712387499423937</v>
+        <v>0.2652639389787579</v>
       </c>
       <c r="J20" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K20" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1298310083255424</v>
+        <v>0.1239713563716557</v>
       </c>
       <c r="M20" t="n">
-        <v>3.902220882228646</v>
+        <v>3.924680677355353</v>
       </c>
       <c r="N20" t="n">
-        <v>27.54695881338682</v>
+        <v>27.85238713627495</v>
       </c>
       <c r="O20" t="n">
-        <v>5.248519678288995</v>
+        <v>5.277536085738775</v>
       </c>
       <c r="P20" t="n">
-        <v>387.7324238347323</v>
+        <v>387.7950982848535</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -37925,28 +38016,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1015416372074639</v>
+        <v>0.09601140251604821</v>
       </c>
       <c r="J21" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K21" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02057196908497771</v>
+        <v>0.01831590836874974</v>
       </c>
       <c r="M21" t="n">
-        <v>3.948603448719903</v>
+        <v>3.966976974849533</v>
       </c>
       <c r="N21" t="n">
-        <v>27.42394993003443</v>
+        <v>27.67565827047251</v>
       </c>
       <c r="O21" t="n">
-        <v>5.236788131100439</v>
+        <v>5.260765939525585</v>
       </c>
       <c r="P21" t="n">
-        <v>390.7132024613272</v>
+        <v>390.7712134043404</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -38007,28 +38098,28 @@
         <v>0.0607</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1680779818265092</v>
+        <v>0.1614737241565821</v>
       </c>
       <c r="J22" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K22" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L22" t="n">
-        <v>0.04582341317083249</v>
+        <v>0.04209019443594342</v>
       </c>
       <c r="M22" t="n">
-        <v>4.277787072670095</v>
+        <v>4.300302785054232</v>
       </c>
       <c r="N22" t="n">
-        <v>33.00716735325983</v>
+        <v>33.38457870209704</v>
       </c>
       <c r="O22" t="n">
-        <v>5.745186450695907</v>
+        <v>5.777938966629627</v>
       </c>
       <c r="P22" t="n">
-        <v>390.5841056299005</v>
+        <v>390.6532841808673</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -38089,28 +38180,28 @@
         <v>0.0672</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1933308973608308</v>
+        <v>0.1841815811390236</v>
       </c>
       <c r="J23" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K23" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L23" t="n">
-        <v>0.04488327642975631</v>
+        <v>0.04033924832012448</v>
       </c>
       <c r="M23" t="n">
-        <v>5.0513738485386</v>
+        <v>5.079675792638102</v>
       </c>
       <c r="N23" t="n">
-        <v>44.62926299963841</v>
+        <v>45.40260959649956</v>
       </c>
       <c r="O23" t="n">
-        <v>6.680513677827358</v>
+        <v>6.73814585746699</v>
       </c>
       <c r="P23" t="n">
-        <v>389.8867852034721</v>
+        <v>389.9826228388574</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -38171,28 +38262,28 @@
         <v>0.0461</v>
       </c>
       <c r="I24" t="n">
-        <v>0.203314851231379</v>
+        <v>0.1939729634636365</v>
       </c>
       <c r="J24" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K24" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L24" t="n">
-        <v>0.04779806962008637</v>
+        <v>0.04308553717542296</v>
       </c>
       <c r="M24" t="n">
-        <v>5.144752701582578</v>
+        <v>5.172238225462753</v>
       </c>
       <c r="N24" t="n">
-        <v>46.20640610003759</v>
+        <v>47.01349066310339</v>
       </c>
       <c r="O24" t="n">
-        <v>6.797529411487499</v>
+        <v>6.85663843753653</v>
       </c>
       <c r="P24" t="n">
-        <v>392.8389421697612</v>
+        <v>392.9367969615281</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -38234,7 +38325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y384"/>
+  <dimension ref="A1:Y385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86973,6 +87064,133 @@
         </is>
       </c>
     </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:05:54+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>-36.78511671540825,175.06688427758635</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>-36.785332359760204,175.0677421599876</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-36.785512122748116,175.0686118920824</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>-36.78575731890627,175.06945918007372</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>-36.78591666663731,175.07033436840416</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>-36.78608259751553,175.07120793144747</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>-36.7862252607435,175.0720882339436</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>-36.78638215202408,175.07294670435138</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>-36.78650941637639,175.07381084680605</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>-36.786636956593554,175.07470032280295</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>-36.78675112425723,175.07559386745677</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>-36.78684704128812,175.07648615908158</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>-36.78694669724711,175.07736962424786</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>-36.787038221128164,175.0782447484041</t>
+        </is>
+      </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>-36.78710746896944,175.07913085221395</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>-36.787170839794356,175.08002568365512</t>
+        </is>
+      </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t>-36.78724943435169,175.08091758187305</t>
+        </is>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>-36.78731028383332,175.0818107385941</t>
+        </is>
+      </c>
+      <c r="T385" t="inlineStr">
+        <is>
+          <t>-36.787369592445465,175.0827056582683</t>
+        </is>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>-36.78742684470659,175.0836012418972</t>
+        </is>
+      </c>
+      <c r="V385" t="inlineStr">
+        <is>
+          <t>-36.78748367291538,175.08449794740713</t>
+        </is>
+      </c>
+      <c r="W385" t="inlineStr">
+        <is>
+          <t>-36.78758866505474,175.0853955163232</t>
+        </is>
+      </c>
+      <c r="X385" t="inlineStr">
+        <is>
+          <t>-36.787661877005675,175.08629450854343</t>
+        </is>
+      </c>
+      <c r="Y385" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0173/nzd0173.xlsx
+++ b/data/nzd0173/nzd0173.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y385"/>
+  <dimension ref="A1:Y387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31641,6 +31641,168 @@
         <v>379.3</v>
       </c>
       <c r="Y385" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>380.18</v>
+      </c>
+      <c r="C386" t="n">
+        <v>377.75</v>
+      </c>
+      <c r="D386" t="n">
+        <v>378.42</v>
+      </c>
+      <c r="E386" t="n">
+        <v>373.83</v>
+      </c>
+      <c r="F386" t="n">
+        <v>374.89</v>
+      </c>
+      <c r="G386" t="n">
+        <v>377.73</v>
+      </c>
+      <c r="H386" t="n">
+        <v>381.67</v>
+      </c>
+      <c r="I386" t="n">
+        <v>385.3</v>
+      </c>
+      <c r="J386" t="n">
+        <v>380.89</v>
+      </c>
+      <c r="K386" t="n">
+        <v>377.13</v>
+      </c>
+      <c r="L386" t="n">
+        <v>376.33</v>
+      </c>
+      <c r="M386" t="n">
+        <v>380.12</v>
+      </c>
+      <c r="N386" t="n">
+        <v>385.38</v>
+      </c>
+      <c r="O386" t="n">
+        <v>384.56</v>
+      </c>
+      <c r="P386" t="n">
+        <v>383.39</v>
+      </c>
+      <c r="Q386" t="n">
+        <v>382.8</v>
+      </c>
+      <c r="R386" t="n">
+        <v>381.69</v>
+      </c>
+      <c r="S386" t="n">
+        <v>380.71</v>
+      </c>
+      <c r="T386" t="n">
+        <v>381.73</v>
+      </c>
+      <c r="U386" t="n">
+        <v>379.13</v>
+      </c>
+      <c r="V386" t="n">
+        <v>378.03</v>
+      </c>
+      <c r="W386" t="n">
+        <v>373.57</v>
+      </c>
+      <c r="X386" t="n">
+        <v>375.78</v>
+      </c>
+      <c r="Y386" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>380.52</v>
+      </c>
+      <c r="C387" t="n">
+        <v>377.04</v>
+      </c>
+      <c r="D387" t="n">
+        <v>378.35</v>
+      </c>
+      <c r="E387" t="n">
+        <v>373.7</v>
+      </c>
+      <c r="F387" t="n">
+        <v>375.63</v>
+      </c>
+      <c r="G387" t="n">
+        <v>377.72</v>
+      </c>
+      <c r="H387" t="n">
+        <v>382.44</v>
+      </c>
+      <c r="I387" t="n">
+        <v>385.48</v>
+      </c>
+      <c r="J387" t="n">
+        <v>381.45</v>
+      </c>
+      <c r="K387" t="n">
+        <v>377.56</v>
+      </c>
+      <c r="L387" t="n">
+        <v>377.03</v>
+      </c>
+      <c r="M387" t="n">
+        <v>381.03</v>
+      </c>
+      <c r="N387" t="n">
+        <v>386.32</v>
+      </c>
+      <c r="O387" t="n">
+        <v>384.81</v>
+      </c>
+      <c r="P387" t="n">
+        <v>384.18</v>
+      </c>
+      <c r="Q387" t="n">
+        <v>383.89</v>
+      </c>
+      <c r="R387" t="n">
+        <v>382.53</v>
+      </c>
+      <c r="S387" t="n">
+        <v>381.14</v>
+      </c>
+      <c r="T387" t="n">
+        <v>381.94</v>
+      </c>
+      <c r="U387" t="n">
+        <v>379.55</v>
+      </c>
+      <c r="V387" t="n">
+        <v>378.92</v>
+      </c>
+      <c r="W387" t="n">
+        <v>374.43</v>
+      </c>
+      <c r="X387" t="n">
+        <v>376.19</v>
+      </c>
+      <c r="Y387" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -31657,7 +31819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B463"/>
+  <dimension ref="A1:B465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36290,6 +36452,26 @@
       </c>
       <c r="B463" t="n">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -36458,28 +36640,28 @@
         <v>0.078</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1183761974341612</v>
+        <v>0.1141475040075202</v>
       </c>
       <c r="J2" t="n">
+        <v>386</v>
+      </c>
+      <c r="K2" t="n">
         <v>384</v>
       </c>
-      <c r="K2" t="n">
-        <v>382</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.03513287715939339</v>
+        <v>0.03294243345656112</v>
       </c>
       <c r="M2" t="n">
-        <v>3.465053795955396</v>
+        <v>3.467640381241954</v>
       </c>
       <c r="N2" t="n">
-        <v>21.65115409677992</v>
+        <v>21.63401013422348</v>
       </c>
       <c r="O2" t="n">
-        <v>4.653080065588805</v>
+        <v>4.651237484178107</v>
       </c>
       <c r="P2" t="n">
-        <v>381.5308296811315</v>
+        <v>381.5752841790916</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -36540,28 +36722,28 @@
         <v>0.0623</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04069311185287491</v>
+        <v>0.03718629829524129</v>
       </c>
       <c r="J3" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K3" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004434444562375295</v>
+        <v>0.003733163792693173</v>
       </c>
       <c r="M3" t="n">
-        <v>3.319552283617357</v>
+        <v>3.319594227172173</v>
       </c>
       <c r="N3" t="n">
-        <v>20.82483061520171</v>
+        <v>20.78280474349152</v>
       </c>
       <c r="O3" t="n">
-        <v>4.563423124716982</v>
+        <v>4.55881615592157</v>
       </c>
       <c r="P3" t="n">
-        <v>379.8953719650088</v>
+        <v>379.9322917015371</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -36622,28 +36804,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02045836786539109</v>
+        <v>0.01642463653560877</v>
       </c>
       <c r="J4" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K4" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001273008734774428</v>
+        <v>0.000825692569648151</v>
       </c>
       <c r="M4" t="n">
-        <v>3.097108199998415</v>
+        <v>3.101323446043701</v>
       </c>
       <c r="N4" t="n">
-        <v>18.39358616840078</v>
+        <v>18.38459420950499</v>
       </c>
       <c r="O4" t="n">
-        <v>4.288774436642801</v>
+        <v>4.287725995152325</v>
       </c>
       <c r="P4" t="n">
-        <v>381.956491607128</v>
+        <v>381.9989567386003</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -36704,28 +36886,28 @@
         <v>0.0529</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1336919485646245</v>
+        <v>0.1300301989862364</v>
       </c>
       <c r="J5" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K5" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04179881788546047</v>
+        <v>0.03991450336569058</v>
       </c>
       <c r="M5" t="n">
-        <v>3.651437957666344</v>
+        <v>3.648736927281558</v>
       </c>
       <c r="N5" t="n">
-        <v>22.95156212563739</v>
+        <v>22.90378534055993</v>
       </c>
       <c r="O5" t="n">
-        <v>4.790778864197073</v>
+        <v>4.785789939034092</v>
       </c>
       <c r="P5" t="n">
-        <v>373.9557033780554</v>
+        <v>373.9942526571207</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -36786,28 +36968,28 @@
         <v>0.0608</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1448594140704455</v>
+        <v>0.1411447981296754</v>
       </c>
       <c r="J6" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K6" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05545883144474018</v>
+        <v>0.05314330322593508</v>
       </c>
       <c r="M6" t="n">
-        <v>3.237139771062067</v>
+        <v>3.237022725744825</v>
       </c>
       <c r="N6" t="n">
-        <v>20.01947418382836</v>
+        <v>19.98964561642004</v>
       </c>
       <c r="O6" t="n">
-        <v>4.474312705190414</v>
+        <v>4.470978149848201</v>
       </c>
       <c r="P6" t="n">
-        <v>375.2137966775907</v>
+        <v>375.2529002023631</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -36868,28 +37050,28 @@
         <v>0.0674</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1163309902817009</v>
+        <v>0.11401449636206</v>
       </c>
       <c r="J7" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K7" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03735152451401669</v>
+        <v>0.03624818118494433</v>
       </c>
       <c r="M7" t="n">
-        <v>3.108454201689568</v>
+        <v>3.102599866428224</v>
       </c>
       <c r="N7" t="n">
-        <v>19.53706340349256</v>
+        <v>19.46429904041912</v>
       </c>
       <c r="O7" t="n">
-        <v>4.420075045006879</v>
+        <v>4.411836243608676</v>
       </c>
       <c r="P7" t="n">
-        <v>377.0039626944755</v>
+        <v>377.0283495303555</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -36950,28 +37132,28 @@
         <v>0.0718</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1441830600104624</v>
+        <v>0.1417337122596079</v>
       </c>
       <c r="J8" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K8" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05356216227897681</v>
+        <v>0.0522941446675298</v>
       </c>
       <c r="M8" t="n">
-        <v>3.256230095653232</v>
+        <v>3.249246974725822</v>
       </c>
       <c r="N8" t="n">
-        <v>20.57650031292535</v>
+        <v>20.50248276890349</v>
       </c>
       <c r="O8" t="n">
-        <v>4.536132748600436</v>
+        <v>4.527966736726706</v>
       </c>
       <c r="P8" t="n">
-        <v>380.736228711373</v>
+        <v>380.7620120786041</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -37032,28 +37214,28 @@
         <v>0.0609</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07728071036885986</v>
+        <v>0.07460081108172176</v>
       </c>
       <c r="J9" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K9" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01705800895865472</v>
+        <v>0.01604880668341635</v>
       </c>
       <c r="M9" t="n">
-        <v>3.105569280514577</v>
+        <v>3.103922360045371</v>
       </c>
       <c r="N9" t="n">
-        <v>19.27750400176511</v>
+        <v>19.21575888969416</v>
       </c>
       <c r="O9" t="n">
-        <v>4.390615446809832</v>
+        <v>4.383578320241827</v>
       </c>
       <c r="P9" t="n">
-        <v>386.0769721998831</v>
+        <v>386.1051842615606</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -37114,28 +37296,28 @@
         <v>0.1019</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08944897938466813</v>
+        <v>0.08616979754991935</v>
       </c>
       <c r="J10" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K10" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02228093748939608</v>
+        <v>0.02086577223379182</v>
       </c>
       <c r="M10" t="n">
-        <v>3.198287680636208</v>
+        <v>3.198741403849388</v>
       </c>
       <c r="N10" t="n">
-        <v>19.66710527203128</v>
+        <v>19.6226449823541</v>
       </c>
       <c r="O10" t="n">
-        <v>4.434761016338004</v>
+        <v>4.429745476023887</v>
       </c>
       <c r="P10" t="n">
-        <v>382.1468921273334</v>
+        <v>382.1814121156707</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -37196,28 +37378,28 @@
         <v>0.0895</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1437307081570878</v>
+        <v>0.1404132141671869</v>
       </c>
       <c r="J11" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K11" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05107283777400462</v>
+        <v>0.04922112170787785</v>
       </c>
       <c r="M11" t="n">
-        <v>3.260033695511018</v>
+        <v>3.257823491224106</v>
       </c>
       <c r="N11" t="n">
-        <v>21.50062379200502</v>
+        <v>21.4478424796873</v>
       </c>
       <c r="O11" t="n">
-        <v>4.636876512481761</v>
+        <v>4.631181542510215</v>
       </c>
       <c r="P11" t="n">
-        <v>376.9234191379217</v>
+        <v>376.9583427909781</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -37278,28 +37460,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1643322059334036</v>
+        <v>0.1584837225403706</v>
       </c>
       <c r="J12" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K12" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L12" t="n">
-        <v>0.08587012841122199</v>
+        <v>0.08029436725864258</v>
       </c>
       <c r="M12" t="n">
-        <v>2.888300437939812</v>
+        <v>2.899493366729454</v>
       </c>
       <c r="N12" t="n">
-        <v>16.10349710142492</v>
+        <v>16.20215283624409</v>
       </c>
       <c r="O12" t="n">
-        <v>4.012916283879458</v>
+        <v>4.025189788847737</v>
       </c>
       <c r="P12" t="n">
-        <v>378.2952450128375</v>
+        <v>378.3568128225558</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -37360,28 +37542,28 @@
         <v>0.0849</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2375665800804572</v>
+        <v>0.2312751170156223</v>
       </c>
       <c r="J13" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K13" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1680993646381777</v>
+        <v>0.1603339527986771</v>
       </c>
       <c r="M13" t="n">
-        <v>2.809347815550699</v>
+        <v>2.825666788400922</v>
       </c>
       <c r="N13" t="n">
-        <v>15.64534399128915</v>
+        <v>15.77533326301883</v>
       </c>
       <c r="O13" t="n">
-        <v>3.955419572092087</v>
+        <v>3.971817375335733</v>
       </c>
       <c r="P13" t="n">
-        <v>380.701621182722</v>
+        <v>380.7678518993064</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -37442,28 +37624,28 @@
         <v>0.0725</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2131854521563736</v>
+        <v>0.2063212509297359</v>
       </c>
       <c r="J14" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K14" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1186337732543218</v>
+        <v>0.1116908903851702</v>
       </c>
       <c r="M14" t="n">
-        <v>3.188202836486211</v>
+        <v>3.206310787059685</v>
       </c>
       <c r="N14" t="n">
-        <v>18.91351427587775</v>
+        <v>19.06662910510525</v>
       </c>
       <c r="O14" t="n">
-        <v>4.34896703550139</v>
+        <v>4.366535137280502</v>
       </c>
       <c r="P14" t="n">
-        <v>387.2069656289814</v>
+        <v>387.2792257260489</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -37524,28 +37706,28 @@
         <v>0.0575</v>
       </c>
       <c r="I15" t="n">
-        <v>0.212273620944569</v>
+        <v>0.2018633354636588</v>
       </c>
       <c r="J15" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K15" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1232563808950256</v>
+        <v>0.1106971293321243</v>
       </c>
       <c r="M15" t="n">
-        <v>3.061949718672672</v>
+        <v>3.103600683720559</v>
       </c>
       <c r="N15" t="n">
-        <v>17.95412725812401</v>
+        <v>18.4360491297655</v>
       </c>
       <c r="O15" t="n">
-        <v>4.237231083871166</v>
+        <v>4.293722060143797</v>
       </c>
       <c r="P15" t="n">
-        <v>389.6821044148364</v>
+        <v>389.7916976158378</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -37606,28 +37788,28 @@
         <v>0.0631</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2254791107759251</v>
+        <v>0.2157809592454531</v>
       </c>
       <c r="J16" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K16" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1265744822235193</v>
+        <v>0.1156586949999882</v>
       </c>
       <c r="M16" t="n">
-        <v>3.197943918040105</v>
+        <v>3.23410812004414</v>
       </c>
       <c r="N16" t="n">
-        <v>19.6517569437334</v>
+        <v>20.04968216372854</v>
       </c>
       <c r="O16" t="n">
-        <v>4.433030221387329</v>
+        <v>4.47768714446739</v>
       </c>
       <c r="P16" t="n">
-        <v>387.7081589757742</v>
+        <v>387.8102537757482</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -37688,28 +37870,28 @@
         <v>0.068</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1844174295706193</v>
+        <v>0.1749233129709736</v>
       </c>
       <c r="J17" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K17" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09551871100626186</v>
+        <v>0.08552309450716478</v>
       </c>
       <c r="M17" t="n">
-        <v>3.00609832524362</v>
+        <v>3.044759870462101</v>
       </c>
       <c r="N17" t="n">
-        <v>18.0394836972288</v>
+        <v>18.4257152309033</v>
       </c>
       <c r="O17" t="n">
-        <v>4.247291336514226</v>
+        <v>4.292518518411225</v>
       </c>
       <c r="P17" t="n">
-        <v>388.14945113086</v>
+        <v>388.2493971832651</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -37770,28 +37952,28 @@
         <v>0.0687</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1880079009683958</v>
+        <v>0.1776116003533106</v>
       </c>
       <c r="J18" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K18" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L18" t="n">
-        <v>0.08676197361825611</v>
+        <v>0.07696205771725972</v>
       </c>
       <c r="M18" t="n">
-        <v>3.289820746324281</v>
+        <v>3.326579621871944</v>
       </c>
       <c r="N18" t="n">
-        <v>20.84086816831965</v>
+        <v>21.30714045771959</v>
       </c>
       <c r="O18" t="n">
-        <v>4.565179971076677</v>
+        <v>4.61596582068364</v>
       </c>
       <c r="P18" t="n">
-        <v>387.7393333867614</v>
+        <v>387.8487778113753</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -37852,28 +38034,28 @@
         <v>0.0696</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2301350532653222</v>
+        <v>0.2177078260806649</v>
       </c>
       <c r="J19" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K19" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1023957785378607</v>
+        <v>0.09091366509877874</v>
       </c>
       <c r="M19" t="n">
-        <v>3.943281436387589</v>
+        <v>3.984231590696357</v>
       </c>
       <c r="N19" t="n">
-        <v>26.00623138162942</v>
+        <v>26.69092819487884</v>
       </c>
       <c r="O19" t="n">
-        <v>5.09963051422644</v>
+        <v>5.166326373244226</v>
       </c>
       <c r="P19" t="n">
-        <v>387.5027354453839</v>
+        <v>387.6335614552344</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -37934,28 +38116,28 @@
         <v>0.0623</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2652639389787579</v>
+        <v>0.2525325244853854</v>
       </c>
       <c r="J20" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K20" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1239713563716557</v>
+        <v>0.1116776529069895</v>
       </c>
       <c r="M20" t="n">
-        <v>3.924680677355353</v>
+        <v>3.973805154767246</v>
       </c>
       <c r="N20" t="n">
-        <v>27.85238713627495</v>
+        <v>28.5679173923946</v>
       </c>
       <c r="O20" t="n">
-        <v>5.277536085738775</v>
+        <v>5.344896387433025</v>
       </c>
       <c r="P20" t="n">
-        <v>387.7950982848535</v>
+        <v>387.9291272028259</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -38016,28 +38198,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.09601140251604821</v>
+        <v>0.08231027822806337</v>
       </c>
       <c r="J21" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K21" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01831590836874974</v>
+        <v>0.01319783343377845</v>
       </c>
       <c r="M21" t="n">
-        <v>3.966976974849533</v>
+        <v>4.017581031909443</v>
       </c>
       <c r="N21" t="n">
-        <v>27.67565827047251</v>
+        <v>28.52825593483119</v>
       </c>
       <c r="O21" t="n">
-        <v>5.260765939525585</v>
+        <v>5.34118488116927</v>
       </c>
       <c r="P21" t="n">
-        <v>390.7712134043404</v>
+        <v>390.9154503298822</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -38098,28 +38280,28 @@
         <v>0.0607</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1614737241565821</v>
+        <v>0.1453517208663207</v>
       </c>
       <c r="J22" t="n">
+        <v>386</v>
+      </c>
+      <c r="K22" t="n">
         <v>384</v>
       </c>
-      <c r="K22" t="n">
-        <v>382</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.04209019443594342</v>
+        <v>0.03338360008209251</v>
       </c>
       <c r="M22" t="n">
-        <v>4.300302785054232</v>
+        <v>4.360922414359597</v>
       </c>
       <c r="N22" t="n">
-        <v>33.38457870209704</v>
+        <v>34.59942534684453</v>
       </c>
       <c r="O22" t="n">
-        <v>5.777938966629627</v>
+        <v>5.88212762075463</v>
       </c>
       <c r="P22" t="n">
-        <v>390.6532841808673</v>
+        <v>390.8227691853212</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -38180,28 +38362,28 @@
         <v>0.0672</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1841815811390236</v>
+        <v>0.1637400819935908</v>
       </c>
       <c r="J23" t="n">
+        <v>386</v>
+      </c>
+      <c r="K23" t="n">
         <v>384</v>
       </c>
-      <c r="K23" t="n">
-        <v>382</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.04033924832012448</v>
+        <v>0.03100139300561144</v>
       </c>
       <c r="M23" t="n">
-        <v>5.079675792638102</v>
+        <v>5.148650086206829</v>
       </c>
       <c r="N23" t="n">
-        <v>45.40260959649956</v>
+        <v>47.39794262658589</v>
       </c>
       <c r="O23" t="n">
-        <v>6.73814585746699</v>
+        <v>6.884616374685367</v>
       </c>
       <c r="P23" t="n">
-        <v>389.9826228388574</v>
+        <v>390.1975179529493</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -38262,28 +38444,28 @@
         <v>0.0461</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1939729634636365</v>
+        <v>0.1723324530519902</v>
       </c>
       <c r="J24" t="n">
+        <v>386</v>
+      </c>
+      <c r="K24" t="n">
         <v>384</v>
       </c>
-      <c r="K24" t="n">
-        <v>382</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.04308553717542296</v>
+        <v>0.03296916624249546</v>
       </c>
       <c r="M24" t="n">
-        <v>5.172238225462753</v>
+        <v>5.244683907265521</v>
       </c>
       <c r="N24" t="n">
-        <v>47.01349066310339</v>
+        <v>49.26903285338847</v>
       </c>
       <c r="O24" t="n">
-        <v>6.85663843753653</v>
+        <v>7.019190327479977</v>
       </c>
       <c r="P24" t="n">
-        <v>392.9367969615281</v>
+        <v>393.1642982266091</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -38325,7 +38507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y385"/>
+  <dimension ref="A1:Y387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87191,6 +87373,260 @@
         </is>
       </c>
     </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>-36.78511706376589,175.06688416253894</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>-36.78533244684972,175.0677421312263</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>-36.78552083171017,175.06860901601308</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>-36.78575487702414,175.06945996941604</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>-36.78593238882509,175.07032941209164</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>-36.78609334759319,175.07120457708936</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>-36.78624231949153,175.07208299568683</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>-36.78638853352165,175.0729452495899</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>-36.78652383356554,175.07380883592853</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>-36.78664017373259,175.07469980543164</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>-36.7867697948333,175.0755900376862</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>-36.78686826476866,175.07648161313094</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>-36.786952846142846,175.07736847870098</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>-36.78705991868688,175.0782420422627</t>
+        </is>
+      </c>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>-36.78713272198668,175.07912855172052</t>
+        </is>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>-36.787200676101634,175.08002296586054</t>
+        </is>
+      </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>-36.787273258895155,175.08091557894082</t>
+        </is>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>-36.78733663836717,175.08180877120247</t>
+        </is>
+      </c>
+      <c r="T386" t="inlineStr">
+        <is>
+          <t>-36.78737930785016,175.0827049564298</t>
+        </is>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>-36.7874545516009,175.083599240568</t>
+        </is>
+      </c>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>-36.787516318706174,175.08449540834903</t>
+        </is>
+      </c>
+      <c r="W386" t="inlineStr">
+        <is>
+          <t>-36.787614768893484,175.08539242825682</t>
+        </is>
+      </c>
+      <c r="X386" t="inlineStr">
+        <is>
+          <t>-36.78769335654409,175.0862896781988</t>
+        </is>
+      </c>
+      <c r="Y386" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>-36.78511410272591,175.066885140442</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>-36.78533863020525,175.0677400891749</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>-36.78552144133753,175.0686088146882</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>-36.785756010755115,175.0694596029357</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>-36.78592592525902,175.07033144968702</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>-36.7860934349922,175.07120454981816</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>-36.78623558347309,175.07208506412692</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>-36.78638693814727,175.0729456132803</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>-36.78651881889106,175.07380953536423</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>-36.78663633103874,175.07470042340293</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>-36.786763571307965,175.07559131427658</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>-36.78686018386186,175.0764833440162</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>-36.78694446938634,175.07737003930106</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>-36.787057677203535,175.0782423218228</t>
+        </is>
+      </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>-36.78712562238397,175.07912919847857</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>-36.787190880446545,175.0800238581487</t>
+        </is>
+      </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>-36.78726570696441,175.08091621383264</t>
+        </is>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>-36.78733277063696,175.08180905993237</t>
+        </is>
+      </c>
+      <c r="T387" t="inlineStr">
+        <is>
+          <t>-36.7873774187437,175.0827050928984</t>
+        </is>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>-36.78745077338805,175.08359951347657</t>
+        </is>
+      </c>
+      <c r="V387" t="inlineStr">
+        <is>
+          <t>-36.78750831464178,175.08449603087308</t>
+        </is>
+      </c>
+      <c r="W387" t="inlineStr">
+        <is>
+          <t>-36.787607054356954,175.0853933408814</t>
+        </is>
+      </c>
+      <c r="X387" t="inlineStr">
+        <is>
+          <t>-36.78768968989332,175.08629024082433</t>
+        </is>
+      </c>
+      <c r="Y387" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0173/nzd0173.xlsx
+++ b/data/nzd0173/nzd0173.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y387"/>
+  <dimension ref="A1:Y388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31803,6 +31803,87 @@
         <v>376.19</v>
       </c>
       <c r="Y387" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>380.1</v>
+      </c>
+      <c r="C388" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="D388" t="n">
+        <v>377.45</v>
+      </c>
+      <c r="E388" t="n">
+        <v>372.77</v>
+      </c>
+      <c r="F388" t="n">
+        <v>374.53</v>
+      </c>
+      <c r="G388" t="n">
+        <v>376.77</v>
+      </c>
+      <c r="H388" t="n">
+        <v>381.33</v>
+      </c>
+      <c r="I388" t="n">
+        <v>384.81</v>
+      </c>
+      <c r="J388" t="n">
+        <v>380.98</v>
+      </c>
+      <c r="K388" t="n">
+        <v>376.59</v>
+      </c>
+      <c r="L388" t="n">
+        <v>377.18</v>
+      </c>
+      <c r="M388" t="n">
+        <v>380.59</v>
+      </c>
+      <c r="N388" t="n">
+        <v>385.49</v>
+      </c>
+      <c r="O388" t="n">
+        <v>385.36</v>
+      </c>
+      <c r="P388" t="n">
+        <v>383.91</v>
+      </c>
+      <c r="Q388" t="n">
+        <v>383.31</v>
+      </c>
+      <c r="R388" t="n">
+        <v>382.27</v>
+      </c>
+      <c r="S388" t="n">
+        <v>381.85</v>
+      </c>
+      <c r="T388" t="n">
+        <v>382.67</v>
+      </c>
+      <c r="U388" t="n">
+        <v>381.04</v>
+      </c>
+      <c r="V388" t="n">
+        <v>380.14</v>
+      </c>
+      <c r="W388" t="n">
+        <v>375.45</v>
+      </c>
+      <c r="X388" t="n">
+        <v>377.34</v>
+      </c>
+      <c r="Y388" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -31819,7 +31900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B465"/>
+  <dimension ref="A1:B466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36472,6 +36553,16 @@
       </c>
       <c r="B465" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>-0.19</v>
       </c>
     </row>
   </sheetData>
@@ -36640,34 +36731,30 @@
         <v>0.078</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1141475040075202</v>
+        <v>0.1119340845697398</v>
       </c>
       <c r="J2" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K2" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03294243345656112</v>
+        <v>0.03180521265560388</v>
       </c>
       <c r="M2" t="n">
-        <v>3.467640381241954</v>
+        <v>3.469483755963616</v>
       </c>
       <c r="N2" t="n">
-        <v>21.63401013422348</v>
+        <v>21.63026464959054</v>
       </c>
       <c r="O2" t="n">
-        <v>4.651237484178107</v>
+        <v>4.650834833617567</v>
       </c>
       <c r="P2" t="n">
-        <v>381.5752841790916</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>381.5986613685856</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>LINESTRING (175.06579065040998 -36.788428024573186, 175.06843500479746 -36.78042091745365)</t>
@@ -36722,34 +36809,30 @@
         <v>0.0623</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03718629829524129</v>
+        <v>0.03501730446126847</v>
       </c>
       <c r="J3" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K3" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003733163792693173</v>
+        <v>0.003321302825617045</v>
       </c>
       <c r="M3" t="n">
-        <v>3.319594227172173</v>
+        <v>3.321697221067767</v>
       </c>
       <c r="N3" t="n">
-        <v>20.78280474349152</v>
+        <v>20.77914328215446</v>
       </c>
       <c r="O3" t="n">
-        <v>4.55881615592157</v>
+        <v>4.558414557952628</v>
       </c>
       <c r="P3" t="n">
-        <v>379.9322917015371</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>379.9552307129744</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>LINESTRING (175.06665563033232 -36.78862224890312, 175.0692999288275 -36.78061513848842)</t>
@@ -36804,34 +36887,30 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01642463653560877</v>
+        <v>0.01397768296504444</v>
       </c>
       <c r="J4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000825692569648151</v>
+        <v>0.0005992242790792135</v>
       </c>
       <c r="M4" t="n">
-        <v>3.101323446043701</v>
+        <v>3.105643633282124</v>
       </c>
       <c r="N4" t="n">
-        <v>18.38459420950499</v>
+        <v>18.40077710904296</v>
       </c>
       <c r="O4" t="n">
-        <v>4.287725995152325</v>
+        <v>4.289612699188933</v>
       </c>
       <c r="P4" t="n">
-        <v>381.9989567386003</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>382.0248354179501</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>LINESTRING (175.06752061025497 -36.788816472740386, 175.07016485285678 -36.780809359031636)</t>
@@ -36886,34 +36965,30 @@
         <v>0.0529</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1300301989862364</v>
+        <v>0.1277314972607445</v>
       </c>
       <c r="J5" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K5" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03991450336569058</v>
+        <v>0.03867505490328327</v>
       </c>
       <c r="M5" t="n">
-        <v>3.648736927281558</v>
+        <v>3.649509068854746</v>
       </c>
       <c r="N5" t="n">
-        <v>22.90378534055993</v>
+        <v>22.90080724695901</v>
       </c>
       <c r="O5" t="n">
-        <v>4.785789939034092</v>
+        <v>4.785478789730345</v>
       </c>
       <c r="P5" t="n">
-        <v>373.9942526571207</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>374.0185634432307</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>LINESTRING (175.06840607129297 -36.789015047195946, 175.07099790277726 -36.7809968967563)</t>
@@ -36968,34 +37043,30 @@
         <v>0.0608</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1411447981296754</v>
+        <v>0.1389483498901134</v>
       </c>
       <c r="J6" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K6" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05314330322593508</v>
+        <v>0.05172029410425372</v>
       </c>
       <c r="M6" t="n">
-        <v>3.237022725744825</v>
+        <v>3.238450643749256</v>
       </c>
       <c r="N6" t="n">
-        <v>19.98964561642004</v>
+        <v>19.98930848093222</v>
       </c>
       <c r="O6" t="n">
-        <v>4.470978149848201</v>
+        <v>4.470940447034853</v>
       </c>
       <c r="P6" t="n">
-        <v>375.2529002023631</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>375.2761295682097</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>LINESTRING (175.06929710886277 -36.7892068798377, 175.07182864133645 -36.78117632194422)</t>
@@ -37050,34 +37121,30 @@
         <v>0.0674</v>
       </c>
       <c r="I7" t="n">
-        <v>0.11401449636206</v>
+        <v>0.1123983485317435</v>
       </c>
       <c r="J7" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K7" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03624818118494433</v>
+        <v>0.03539553485804314</v>
       </c>
       <c r="M7" t="n">
-        <v>3.102599866428224</v>
+        <v>3.101641000340207</v>
       </c>
       <c r="N7" t="n">
-        <v>19.46429904041912</v>
+        <v>19.44178613759182</v>
       </c>
       <c r="O7" t="n">
-        <v>4.411836243608676</v>
+        <v>4.409284084473557</v>
       </c>
       <c r="P7" t="n">
-        <v>377.0283495303555</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>377.0454417106019</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>LINESTRING (175.07017442074223 -36.789394666271015, 175.07268168886017 -36.78135920845034)</t>
@@ -37132,34 +37199,30 @@
         <v>0.0718</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1417337122596079</v>
+        <v>0.140162240767956</v>
       </c>
       <c r="J8" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K8" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0522941446675298</v>
+        <v>0.05139520445329693</v>
       </c>
       <c r="M8" t="n">
-        <v>3.249246974725822</v>
+        <v>3.247108961724396</v>
       </c>
       <c r="N8" t="n">
-        <v>20.50248276890349</v>
+        <v>20.47577243124025</v>
       </c>
       <c r="O8" t="n">
-        <v>4.527966736726706</v>
+        <v>4.525016290715454</v>
       </c>
       <c r="P8" t="n">
-        <v>380.7620120786041</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>380.7786317673996</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>LINESTRING (175.07105767964904 -36.78958119369445, 175.07352739859778 -36.78153824755125)</t>
@@ -37214,34 +37277,30 @@
         <v>0.0609</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07460081108172176</v>
+        <v>0.07298972590738066</v>
       </c>
       <c r="J9" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K9" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01604880668341635</v>
+        <v>0.01543212073596045</v>
       </c>
       <c r="M9" t="n">
-        <v>3.103922360045371</v>
+        <v>3.104632785785274</v>
       </c>
       <c r="N9" t="n">
-        <v>19.21575888969416</v>
+        <v>19.19371442258824</v>
       </c>
       <c r="O9" t="n">
-        <v>4.383578320241827</v>
+        <v>4.381063161218774</v>
       </c>
       <c r="P9" t="n">
-        <v>386.1051842615606</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>386.1222228997814</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>LINESTRING (175.07216671905078 -36.7898035186562, 175.07402425825438 -36.781655058097314)</t>
@@ -37296,34 +37355,30 @@
         <v>0.1019</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08616979754991935</v>
+        <v>0.0844554869718333</v>
       </c>
       <c r="J10" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K10" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02086577223379182</v>
+        <v>0.02013313231918068</v>
       </c>
       <c r="M10" t="n">
-        <v>3.198741403849388</v>
+        <v>3.199277121755058</v>
       </c>
       <c r="N10" t="n">
-        <v>19.6226449823541</v>
+        <v>19.6032003516734</v>
       </c>
       <c r="O10" t="n">
-        <v>4.429745476023887</v>
+        <v>4.427550152361167</v>
       </c>
       <c r="P10" t="n">
-        <v>382.1814121156707</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>382.199542453038</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>LINESTRING (175.0733330897094 -36.78993461693664, 175.07448130862855 -36.78170222048105)</t>
@@ -37378,34 +37433,30 @@
         <v>0.0895</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1404132141671869</v>
+        <v>0.1384025567554391</v>
       </c>
       <c r="J11" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K11" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04922112170787785</v>
+        <v>0.04803867072188583</v>
       </c>
       <c r="M11" t="n">
-        <v>3.257823491224106</v>
+        <v>3.25848155724858</v>
       </c>
       <c r="N11" t="n">
-        <v>21.4478424796873</v>
+        <v>21.43542327990939</v>
       </c>
       <c r="O11" t="n">
-        <v>4.631181542510215</v>
+        <v>4.629840524241563</v>
       </c>
       <c r="P11" t="n">
-        <v>376.9583427909781</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>376.9796072559304</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>LINESTRING (175.07415779559986 -36.79001039359068, 175.07547899054856 -36.781794750795775)</t>
@@ -37460,34 +37511,30 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1584837225403706</v>
+        <v>0.155839363470923</v>
       </c>
       <c r="J12" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K12" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L12" t="n">
-        <v>0.08029436725864258</v>
+        <v>0.07789455205439288</v>
       </c>
       <c r="M12" t="n">
-        <v>2.899493366729454</v>
+        <v>2.903734852009133</v>
       </c>
       <c r="N12" t="n">
-        <v>16.20215283624409</v>
+        <v>16.23466560115448</v>
       </c>
       <c r="O12" t="n">
-        <v>4.025189788847737</v>
+        <v>4.029226427138897</v>
       </c>
       <c r="P12" t="n">
-        <v>378.3568128225558</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>378.3847792381297</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>LINESTRING (175.07490369797438 -36.790115649037105, 175.07658028819932 -36.78194193738602)</t>
@@ -37542,34 +37589,30 @@
         <v>0.0849</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2312751170156223</v>
+        <v>0.2281722896580625</v>
       </c>
       <c r="J13" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K13" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1603339527986771</v>
+        <v>0.1565729058614561</v>
       </c>
       <c r="M13" t="n">
-        <v>2.825666788400922</v>
+        <v>2.83421586851881</v>
       </c>
       <c r="N13" t="n">
-        <v>15.77533326301883</v>
+        <v>15.83697567861955</v>
       </c>
       <c r="O13" t="n">
-        <v>3.971817375335733</v>
+        <v>3.979569785619992</v>
       </c>
       <c r="P13" t="n">
-        <v>380.7678518993064</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>380.8006670189844</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>LINESTRING (175.07575856931484 -36.79024377287137, 175.07750721552364 -36.782079811310595)</t>
@@ -37624,34 +37667,30 @@
         <v>0.0725</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2063212509297359</v>
+        <v>0.2027522717130071</v>
       </c>
       <c r="J14" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K14" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1116908903851702</v>
+        <v>0.1081009057863276</v>
       </c>
       <c r="M14" t="n">
-        <v>3.206310787059685</v>
+        <v>3.216108323000881</v>
       </c>
       <c r="N14" t="n">
-        <v>19.06662910510525</v>
+        <v>19.15284791925669</v>
       </c>
       <c r="O14" t="n">
-        <v>4.366535137280502</v>
+        <v>4.376396682118372</v>
       </c>
       <c r="P14" t="n">
-        <v>387.2792257260489</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>387.3169708103313</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>LINESTRING (175.07672864086882 -36.79038713632437, 175.07825492200774 -36.78219446792616)</t>
@@ -37706,34 +37745,30 @@
         <v>0.0575</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2018633354636588</v>
+        <v>0.1970568426630117</v>
       </c>
       <c r="J15" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K15" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1106971293321243</v>
+        <v>0.1052865854845427</v>
       </c>
       <c r="M15" t="n">
-        <v>3.103600683720559</v>
+        <v>3.122728853497639</v>
       </c>
       <c r="N15" t="n">
-        <v>18.4360491297655</v>
+        <v>18.63414454236146</v>
       </c>
       <c r="O15" t="n">
-        <v>4.293722060143797</v>
+        <v>4.316728453627986</v>
       </c>
       <c r="P15" t="n">
-        <v>389.7916976158378</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>389.8425304912476</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>LINESTRING (175.0778119961178 -36.79050785689815, 175.07884000751338 -36.7822652533793)</t>
@@ -37788,34 +37823,30 @@
         <v>0.0631</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2157809592454531</v>
+        <v>0.2110538411812319</v>
       </c>
       <c r="J16" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K16" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1156586949999882</v>
+        <v>0.1105612356879111</v>
       </c>
       <c r="M16" t="n">
-        <v>3.23410812004414</v>
+        <v>3.252147635426451</v>
       </c>
       <c r="N16" t="n">
-        <v>20.04968216372854</v>
+        <v>20.23555886954621</v>
       </c>
       <c r="O16" t="n">
-        <v>4.47768714446739</v>
+        <v>4.498395143775856</v>
       </c>
       <c r="P16" t="n">
-        <v>387.8102537757482</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>387.8602471937292</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>LINESTRING (175.0788146672156 -36.790578185229045, 175.07956728522515 -36.78231642641688)</t>
@@ -37870,34 +37901,30 @@
         <v>0.068</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1749233129709736</v>
+        <v>0.1702173217692964</v>
       </c>
       <c r="J17" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K17" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L17" t="n">
-        <v>0.08552309450716478</v>
+        <v>0.08079823857852697</v>
       </c>
       <c r="M17" t="n">
-        <v>3.044759870462101</v>
+        <v>3.064181706006159</v>
       </c>
       <c r="N17" t="n">
-        <v>18.4257152309033</v>
+        <v>18.61366841780672</v>
       </c>
       <c r="O17" t="n">
-        <v>4.292518518411225</v>
+        <v>4.314356083798221</v>
       </c>
       <c r="P17" t="n">
-        <v>388.2493971832651</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>388.299167166152</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>LINESTRING (175.07970959046943 -36.790640837365046, 175.0804621456757 -36.782379079598655)</t>
@@ -37952,34 +37979,30 @@
         <v>0.0687</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1776116003533106</v>
+        <v>0.1725582835437614</v>
       </c>
       <c r="J18" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K18" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L18" t="n">
-        <v>0.07696205771725972</v>
+        <v>0.07246069086843898</v>
       </c>
       <c r="M18" t="n">
-        <v>3.326579621871944</v>
+        <v>3.344584090412146</v>
       </c>
       <c r="N18" t="n">
-        <v>21.30714045771959</v>
+        <v>21.52370298539925</v>
       </c>
       <c r="O18" t="n">
-        <v>4.61596582068364</v>
+        <v>4.639364502321332</v>
       </c>
       <c r="P18" t="n">
-        <v>387.8487778113753</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>387.9022210670795</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>LINESTRING (175.08062707943563 -36.79070480140889, 175.08132191111184 -36.78243978857827)</t>
@@ -38034,34 +38057,30 @@
         <v>0.0696</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2177078260806649</v>
+        <v>0.2120271649392037</v>
       </c>
       <c r="J19" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K19" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L19" t="n">
-        <v>0.09091366509877874</v>
+        <v>0.08604390623965308</v>
       </c>
       <c r="M19" t="n">
-        <v>3.984231590696357</v>
+        <v>4.002830011483678</v>
       </c>
       <c r="N19" t="n">
-        <v>26.69092819487884</v>
+        <v>26.9652058276371</v>
       </c>
       <c r="O19" t="n">
-        <v>5.166326373244226</v>
+        <v>5.192803272572252</v>
       </c>
       <c r="P19" t="n">
-        <v>387.6335614552344</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>387.693639427266</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>LINESTRING (175.0815531301122 -36.79076101792391, 175.08217040966323 -36.78249204114308)</t>
@@ -38116,34 +38135,30 @@
         <v>0.0623</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2525325244853854</v>
+        <v>0.2466578258229886</v>
       </c>
       <c r="J20" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K20" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1116776529069895</v>
+        <v>0.1063764771703131</v>
       </c>
       <c r="M20" t="n">
-        <v>3.973805154767246</v>
+        <v>3.996193836637018</v>
       </c>
       <c r="N20" t="n">
-        <v>28.5679173923946</v>
+        <v>28.86119432418844</v>
       </c>
       <c r="O20" t="n">
-        <v>5.344896387433025</v>
+        <v>5.372261565131433</v>
       </c>
       <c r="P20" t="n">
-        <v>387.9291272028259</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>387.9912572917619</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>LINESTRING (175.08245688161998 -36.790813252782236, 175.08305429093673 -36.78254333936692)</t>
@@ -38198,34 +38213,30 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08231027822806337</v>
+        <v>0.07639005482467935</v>
       </c>
       <c r="J21" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K21" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01319783343377845</v>
+        <v>0.01130181564569477</v>
       </c>
       <c r="M21" t="n">
-        <v>4.017581031909443</v>
+        <v>4.03807390784397</v>
       </c>
       <c r="N21" t="n">
-        <v>28.52825593483119</v>
+        <v>28.82734685957746</v>
       </c>
       <c r="O21" t="n">
-        <v>5.34118488116927</v>
+        <v>5.369110434660239</v>
       </c>
       <c r="P21" t="n">
-        <v>390.9154503298822</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>390.9780618828675</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>LINESTRING (175.08335288131428 -36.790865107535026, 175.0839502276395 -36.78259519552579)</t>
@@ -38280,34 +38291,30 @@
         <v>0.0607</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1453517208663207</v>
+        <v>0.1382162420576701</v>
       </c>
       <c r="J22" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K22" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L22" t="n">
-        <v>0.03338360008209251</v>
+        <v>0.02997965178834205</v>
       </c>
       <c r="M22" t="n">
-        <v>4.360922414359597</v>
+        <v>4.387145206866652</v>
       </c>
       <c r="N22" t="n">
-        <v>34.59942534684453</v>
+        <v>35.05460800884817</v>
       </c>
       <c r="O22" t="n">
-        <v>5.88212762075463</v>
+        <v>5.92069320340517</v>
       </c>
       <c r="P22" t="n">
-        <v>390.8227691853212</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>390.8981310608851</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>LINESTRING (175.08423098144848 -36.79091606670379, 175.08487400142928 -36.78264836785435)</t>
@@ -38362,34 +38369,30 @@
         <v>0.0672</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1637400819935908</v>
+        <v>0.1543705125051966</v>
       </c>
       <c r="J23" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K23" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L23" t="n">
-        <v>0.03100139300561144</v>
+        <v>0.02726571301107616</v>
       </c>
       <c r="M23" t="n">
-        <v>5.148650086206829</v>
+        <v>5.180957724828112</v>
       </c>
       <c r="N23" t="n">
-        <v>47.39794262658589</v>
+        <v>48.21462020274139</v>
       </c>
       <c r="O23" t="n">
-        <v>6.884616374685367</v>
+        <v>6.943674834174004</v>
       </c>
       <c r="P23" t="n">
-        <v>390.1975179529493</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>390.2964753388245</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>LINESTRING (175.08499598519694 -36.790965836970074, 175.08597154604738 -36.78271915962405)</t>
@@ -38444,34 +38447,30 @@
         <v>0.0461</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1723324530519902</v>
+        <v>0.1623220235865206</v>
       </c>
       <c r="J24" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K24" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L24" t="n">
-        <v>0.03296916624249546</v>
+        <v>0.02889809736005</v>
       </c>
       <c r="M24" t="n">
-        <v>5.244683907265521</v>
+        <v>5.279211870176684</v>
       </c>
       <c r="N24" t="n">
-        <v>49.26903285338847</v>
+        <v>50.2138064843864</v>
       </c>
       <c r="O24" t="n">
-        <v>7.019190327479977</v>
+        <v>7.086170085764693</v>
       </c>
       <c r="P24" t="n">
-        <v>393.1642982266091</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>393.2700241014871</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>LINESTRING (175.08577399226172 -36.791053974821686, 175.08703552937925 -36.78283235592655)</t>
@@ -38507,7 +38506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y387"/>
+  <dimension ref="A1:Y388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87627,6 +87626,133 @@
         </is>
       </c>
     </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>-36.785117760481185,175.06688393244409</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>-36.78534333303902,175.06773853606515</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>-36.785529279403335,175.06860622622523</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>-36.78576412129221,175.06945698119128</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>-36.785935533262624,175.0703284208289</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>-36.78610173789767,175.07120195905318</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>-36.786245293837304,175.07208208234954</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>-36.78639287648528,175.07294425954376</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>-36.78652302763573,175.07380894833784</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>-36.78664499944117,175.07469902937459</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>-36.786762237695385,175.07559158783164</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>-36.78686409111351,175.07648250710469</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>-36.786951865884106,175.0773686613244</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>-36.787052745940194,175.07824293685502</t>
+        </is>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>-36.78712804883047,175.0791289774347</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>-36.78719609281349,175.0800233833532</t>
+        </is>
+      </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>-36.78726804446678,175.08091601731851</t>
+        </is>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>-36.787326384384734,175.08180953667238</t>
+        </is>
+      </c>
+      <c r="T388" t="inlineStr">
+        <is>
+          <t>-36.78737085184978,175.08270556728925</t>
+        </is>
+      </c>
+      <c r="U388" t="inlineStr">
+        <is>
+          <t>-36.78743736972813,175.08360048165213</t>
+        </is>
+      </c>
+      <c r="V388" t="inlineStr">
+        <is>
+          <t>-36.78749734277822,175.08449688422044</t>
+        </is>
+      </c>
+      <c r="W388" t="inlineStr">
+        <is>
+          <t>-36.787597904557806,175.08539442329644</t>
+        </is>
+      </c>
+      <c r="X388" t="inlineStr">
+        <is>
+          <t>-36.78767940538504,175.08629181892013</t>
+        </is>
+      </c>
+      <c r="Y388" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0173/nzd0173.xlsx
+++ b/data/nzd0173/nzd0173.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y388"/>
+  <dimension ref="A1:Y389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31884,6 +31884,87 @@
         <v>377.34</v>
       </c>
       <c r="Y388" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>380.6</v>
+      </c>
+      <c r="C389" t="n">
+        <v>377.5</v>
+      </c>
+      <c r="D389" t="n">
+        <v>378.17</v>
+      </c>
+      <c r="E389" t="n">
+        <v>373.89</v>
+      </c>
+      <c r="F389" t="n">
+        <v>375.62</v>
+      </c>
+      <c r="G389" t="n">
+        <v>377.54</v>
+      </c>
+      <c r="H389" t="n">
+        <v>382.25</v>
+      </c>
+      <c r="I389" t="n">
+        <v>385.88</v>
+      </c>
+      <c r="J389" t="n">
+        <v>381.92</v>
+      </c>
+      <c r="K389" t="n">
+        <v>377.22</v>
+      </c>
+      <c r="L389" t="n">
+        <v>377.59</v>
+      </c>
+      <c r="M389" t="n">
+        <v>381.36</v>
+      </c>
+      <c r="N389" t="n">
+        <v>386.47</v>
+      </c>
+      <c r="O389" t="n">
+        <v>386.61</v>
+      </c>
+      <c r="P389" t="n">
+        <v>386.19</v>
+      </c>
+      <c r="Q389" t="n">
+        <v>385.43</v>
+      </c>
+      <c r="R389" t="n">
+        <v>383.73</v>
+      </c>
+      <c r="S389" t="n">
+        <v>383.64</v>
+      </c>
+      <c r="T389" t="n">
+        <v>385.88</v>
+      </c>
+      <c r="U389" t="n">
+        <v>384.92</v>
+      </c>
+      <c r="V389" t="n">
+        <v>382.04</v>
+      </c>
+      <c r="W389" t="n">
+        <v>382.6</v>
+      </c>
+      <c r="X389" t="n">
+        <v>384.88</v>
+      </c>
+      <c r="Y389" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -31900,7 +31981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B466"/>
+  <dimension ref="A1:B467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36563,6 +36644,16 @@
       </c>
       <c r="B466" t="n">
         <v>-0.19</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>-0.68</v>
       </c>
     </row>
   </sheetData>
@@ -36731,28 +36822,28 @@
         <v>0.078</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1119340845697398</v>
+        <v>0.1099899689686221</v>
       </c>
       <c r="J2" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K2" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03180521265560388</v>
+        <v>0.0308447971105017</v>
       </c>
       <c r="M2" t="n">
-        <v>3.469483755963616</v>
+        <v>3.470111505535109</v>
       </c>
       <c r="N2" t="n">
-        <v>21.63026464959054</v>
+        <v>21.61489114946995</v>
       </c>
       <c r="O2" t="n">
-        <v>4.650834833617567</v>
+        <v>4.649181772040103</v>
       </c>
       <c r="P2" t="n">
-        <v>381.5986613685856</v>
+        <v>381.6192362003546</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36809,28 +36900,28 @@
         <v>0.0623</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03501730446126847</v>
+        <v>0.03336235470297361</v>
       </c>
       <c r="J3" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K3" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003321302825617045</v>
+        <v>0.003027371014764357</v>
       </c>
       <c r="M3" t="n">
-        <v>3.321697221067767</v>
+        <v>3.321298154385288</v>
       </c>
       <c r="N3" t="n">
-        <v>20.77914328215446</v>
+        <v>20.754867783505</v>
       </c>
       <c r="O3" t="n">
-        <v>4.558414557952628</v>
+        <v>4.55575106689391</v>
       </c>
       <c r="P3" t="n">
-        <v>379.9552307129744</v>
+        <v>379.9727686777441</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36887,28 +36978,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01397768296504444</v>
+        <v>0.0119109625005747</v>
       </c>
       <c r="J4" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K4" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005992242790792135</v>
+        <v>0.0004364139124232169</v>
       </c>
       <c r="M4" t="n">
-        <v>3.105643633282124</v>
+        <v>3.108048587084206</v>
       </c>
       <c r="N4" t="n">
-        <v>18.40077710904296</v>
+        <v>18.39901390828885</v>
       </c>
       <c r="O4" t="n">
-        <v>4.289612699188933</v>
+        <v>4.289407174457661</v>
       </c>
       <c r="P4" t="n">
-        <v>382.0248354179501</v>
+        <v>382.0467370318892</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36965,28 +37056,28 @@
         <v>0.0529</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1277314972607445</v>
+        <v>0.1260039614692125</v>
       </c>
       <c r="J5" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K5" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03867505490328327</v>
+        <v>0.03781631304122413</v>
       </c>
       <c r="M5" t="n">
-        <v>3.649509068854746</v>
+        <v>3.647779950021959</v>
       </c>
       <c r="N5" t="n">
-        <v>22.90080724695901</v>
+        <v>22.87368821725551</v>
       </c>
       <c r="O5" t="n">
-        <v>4.785478789730345</v>
+        <v>4.782644479496203</v>
       </c>
       <c r="P5" t="n">
-        <v>374.0185634432307</v>
+        <v>374.0368706224659</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37043,28 +37134,28 @@
         <v>0.0608</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1389483498901134</v>
+        <v>0.1373080551498483</v>
       </c>
       <c r="J6" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K6" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05172029410425372</v>
+        <v>0.05075249614364197</v>
       </c>
       <c r="M6" t="n">
-        <v>3.238450643749256</v>
+        <v>3.237501181064756</v>
       </c>
       <c r="N6" t="n">
-        <v>19.98930848093222</v>
+        <v>19.96655238843507</v>
       </c>
       <c r="O6" t="n">
-        <v>4.470940447034853</v>
+        <v>4.468394833543146</v>
       </c>
       <c r="P6" t="n">
-        <v>375.2761295682097</v>
+        <v>375.2935122296606</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37121,28 +37212,28 @@
         <v>0.0674</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1123983485317435</v>
+        <v>0.111178400044173</v>
       </c>
       <c r="J7" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K7" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03539553485804314</v>
+        <v>0.03480745100300775</v>
       </c>
       <c r="M7" t="n">
-        <v>3.101641000340207</v>
+        <v>3.098936050755808</v>
       </c>
       <c r="N7" t="n">
-        <v>19.44178613759182</v>
+        <v>19.40758841697819</v>
       </c>
       <c r="O7" t="n">
-        <v>4.409284084473557</v>
+        <v>4.405404455549818</v>
       </c>
       <c r="P7" t="n">
-        <v>377.0454417106019</v>
+        <v>377.0583698454222</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37199,28 +37290,28 @@
         <v>0.0718</v>
       </c>
       <c r="I8" t="n">
-        <v>0.140162240767956</v>
+        <v>0.1390559574322966</v>
       </c>
       <c r="J8" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K8" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05139520445329693</v>
+        <v>0.05085160320853821</v>
       </c>
       <c r="M8" t="n">
-        <v>3.247108961724396</v>
+        <v>3.243245837981795</v>
       </c>
       <c r="N8" t="n">
-        <v>20.47577243124025</v>
+        <v>20.43608318120838</v>
       </c>
       <c r="O8" t="n">
-        <v>4.525016290715454</v>
+        <v>4.520628626773978</v>
       </c>
       <c r="P8" t="n">
-        <v>380.7786317673996</v>
+        <v>380.7903553608615</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37277,28 +37368,28 @@
         <v>0.0609</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07298972590738066</v>
+        <v>0.07192343767316778</v>
       </c>
       <c r="J9" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K9" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01543212073596045</v>
+        <v>0.01506002600261547</v>
       </c>
       <c r="M9" t="n">
-        <v>3.104632785785274</v>
+        <v>3.1024246762064</v>
       </c>
       <c r="N9" t="n">
-        <v>19.19371442258824</v>
+        <v>19.15640054906818</v>
       </c>
       <c r="O9" t="n">
-        <v>4.381063161218774</v>
+        <v>4.3768025485585</v>
       </c>
       <c r="P9" t="n">
-        <v>386.1222228997814</v>
+        <v>386.1335226539838</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37355,28 +37446,28 @@
         <v>0.1019</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0844554869718333</v>
+        <v>0.08321899709504206</v>
       </c>
       <c r="J10" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K10" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02013313231918068</v>
+        <v>0.01964483081044599</v>
       </c>
       <c r="M10" t="n">
-        <v>3.199277121755058</v>
+        <v>3.197381959197454</v>
       </c>
       <c r="N10" t="n">
-        <v>19.6032003516734</v>
+        <v>19.56902098960251</v>
       </c>
       <c r="O10" t="n">
-        <v>4.427550152361167</v>
+        <v>4.42368861806553</v>
       </c>
       <c r="P10" t="n">
-        <v>382.199542453038</v>
+        <v>382.2126458815794</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37433,28 +37524,28 @@
         <v>0.0895</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1384025567554391</v>
+        <v>0.1367171262107104</v>
       </c>
       <c r="J11" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K11" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04803867072188583</v>
+        <v>0.04710346598361204</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25848155724858</v>
+        <v>3.25763882610016</v>
       </c>
       <c r="N11" t="n">
-        <v>21.43542327990939</v>
+        <v>21.4105447882842</v>
       </c>
       <c r="O11" t="n">
-        <v>4.629840524241563</v>
+        <v>4.627152989504907</v>
       </c>
       <c r="P11" t="n">
-        <v>376.9796072559304</v>
+        <v>376.9974682341063</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37511,28 +37602,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.155839363470923</v>
+        <v>0.1534234160993966</v>
       </c>
       <c r="J12" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K12" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07789455205439288</v>
+        <v>0.07578003074006678</v>
       </c>
       <c r="M12" t="n">
-        <v>2.903734852009133</v>
+        <v>2.906907672594703</v>
       </c>
       <c r="N12" t="n">
-        <v>16.23466560115448</v>
+        <v>16.25522035731352</v>
       </c>
       <c r="O12" t="n">
-        <v>4.029226427138897</v>
+        <v>4.031776327788227</v>
       </c>
       <c r="P12" t="n">
-        <v>378.3847792381297</v>
+        <v>378.4103817071321</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37589,28 +37680,28 @@
         <v>0.0849</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2281722896580625</v>
+        <v>0.2254777141362868</v>
       </c>
       <c r="J13" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K13" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1565729058614561</v>
+        <v>0.1535103319573698</v>
       </c>
       <c r="M13" t="n">
-        <v>2.83421586851881</v>
+        <v>2.840874592440692</v>
       </c>
       <c r="N13" t="n">
-        <v>15.83697567861955</v>
+        <v>15.87377758898001</v>
       </c>
       <c r="O13" t="n">
-        <v>3.979569785619992</v>
+        <v>3.98419095789597</v>
       </c>
       <c r="P13" t="n">
-        <v>380.8006670189844</v>
+        <v>380.829222188308</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37667,28 +37758,28 @@
         <v>0.0725</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2027522717130071</v>
+        <v>0.1996974882238712</v>
       </c>
       <c r="J14" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K14" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1081009057863276</v>
+        <v>0.1052151430882647</v>
       </c>
       <c r="M14" t="n">
-        <v>3.216108323000881</v>
+        <v>3.223447546231884</v>
       </c>
       <c r="N14" t="n">
-        <v>19.15284791925669</v>
+        <v>19.20324283193285</v>
       </c>
       <c r="O14" t="n">
-        <v>4.376396682118372</v>
+        <v>4.382150480293078</v>
       </c>
       <c r="P14" t="n">
-        <v>387.3169708103313</v>
+        <v>387.3493432040811</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37745,28 +37836,28 @@
         <v>0.0575</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1970568426630117</v>
+        <v>0.1929099923638954</v>
       </c>
       <c r="J15" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K15" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1052865854845427</v>
+        <v>0.1009317820129122</v>
       </c>
       <c r="M15" t="n">
-        <v>3.122728853497639</v>
+        <v>3.138722904712612</v>
       </c>
       <c r="N15" t="n">
-        <v>18.63414454236146</v>
+        <v>18.76995129882493</v>
       </c>
       <c r="O15" t="n">
-        <v>4.316728453627986</v>
+        <v>4.332430183952758</v>
       </c>
       <c r="P15" t="n">
-        <v>389.8425304912476</v>
+        <v>389.8864758219663</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37823,28 +37914,28 @@
         <v>0.0631</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2110538411812319</v>
+        <v>0.2074883577446348</v>
       </c>
       <c r="J16" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K16" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1105612356879111</v>
+        <v>0.1071178214635822</v>
       </c>
       <c r="M16" t="n">
-        <v>3.252147635426451</v>
+        <v>3.263700171670611</v>
       </c>
       <c r="N16" t="n">
-        <v>20.23555886954621</v>
+        <v>20.31930659334192</v>
       </c>
       <c r="O16" t="n">
-        <v>4.498395143775856</v>
+        <v>4.507694154813736</v>
       </c>
       <c r="P16" t="n">
-        <v>387.8602471937292</v>
+        <v>387.8980316174463</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37901,28 +37992,28 @@
         <v>0.068</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1702173217692964</v>
+        <v>0.1666007758064643</v>
       </c>
       <c r="J17" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K17" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L17" t="n">
-        <v>0.08079823857852697</v>
+        <v>0.07750625499383856</v>
       </c>
       <c r="M17" t="n">
-        <v>3.064181706006159</v>
+        <v>3.077618305836726</v>
       </c>
       <c r="N17" t="n">
-        <v>18.61366841780672</v>
+        <v>18.70551672239434</v>
       </c>
       <c r="O17" t="n">
-        <v>4.314356083798221</v>
+        <v>4.324987482339613</v>
       </c>
       <c r="P17" t="n">
-        <v>388.299167166152</v>
+        <v>388.3374927137199</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37979,28 +38070,28 @@
         <v>0.0687</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1725582835437614</v>
+        <v>0.1682734227760594</v>
       </c>
       <c r="J18" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K18" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L18" t="n">
-        <v>0.07246069086843898</v>
+        <v>0.06890715577504014</v>
       </c>
       <c r="M18" t="n">
-        <v>3.344584090412146</v>
+        <v>3.358570760382905</v>
       </c>
       <c r="N18" t="n">
-        <v>21.52370298539925</v>
+        <v>21.66450225139452</v>
       </c>
       <c r="O18" t="n">
-        <v>4.639364502321332</v>
+        <v>4.654514179954178</v>
       </c>
       <c r="P18" t="n">
-        <v>387.9022210670795</v>
+        <v>387.9476289332763</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -38057,28 +38148,28 @@
         <v>0.0696</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2120271649392037</v>
+        <v>0.2072827910395877</v>
       </c>
       <c r="J19" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K19" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L19" t="n">
-        <v>0.08604390623965308</v>
+        <v>0.08227655965542047</v>
       </c>
       <c r="M19" t="n">
-        <v>4.002830011483678</v>
+        <v>4.017314459480431</v>
       </c>
       <c r="N19" t="n">
-        <v>26.9652058276371</v>
+        <v>27.13633486766746</v>
       </c>
       <c r="O19" t="n">
-        <v>5.192803272572252</v>
+        <v>5.209254732461013</v>
       </c>
       <c r="P19" t="n">
-        <v>387.693639427266</v>
+        <v>387.7439168824509</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -38135,28 +38226,28 @@
         <v>0.0623</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2466578258229886</v>
+        <v>0.2424127058973381</v>
       </c>
       <c r="J20" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K20" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1063764771703131</v>
+        <v>0.102992490986245</v>
       </c>
       <c r="M20" t="n">
-        <v>3.996193836637018</v>
+        <v>4.0097211449269</v>
       </c>
       <c r="N20" t="n">
-        <v>28.86119432418844</v>
+        <v>28.97945866811274</v>
       </c>
       <c r="O20" t="n">
-        <v>5.372261565131433</v>
+        <v>5.383257254498687</v>
       </c>
       <c r="P20" t="n">
-        <v>387.9912572917619</v>
+        <v>388.036244013157</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -38213,28 +38304,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.07639005482467935</v>
+        <v>0.07243453308328489</v>
       </c>
       <c r="J21" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K21" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01130181564569477</v>
+        <v>0.01016807709817569</v>
       </c>
       <c r="M21" t="n">
-        <v>4.03807390784397</v>
+        <v>4.048420067687102</v>
       </c>
       <c r="N21" t="n">
-        <v>28.82734685957746</v>
+        <v>28.92031033935304</v>
       </c>
       <c r="O21" t="n">
-        <v>5.369110434660239</v>
+        <v>5.37776071793391</v>
       </c>
       <c r="P21" t="n">
-        <v>390.9780618828675</v>
+        <v>391.0199796514274</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -38291,28 +38382,28 @@
         <v>0.0607</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1382162420576701</v>
+        <v>0.1320897521270053</v>
       </c>
       <c r="J22" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K22" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02997965178834205</v>
+        <v>0.02728681415700585</v>
       </c>
       <c r="M22" t="n">
-        <v>4.387145206866652</v>
+        <v>4.408005933017304</v>
       </c>
       <c r="N22" t="n">
-        <v>35.05460800884817</v>
+        <v>35.36760899009226</v>
       </c>
       <c r="O22" t="n">
-        <v>5.92069320340517</v>
+        <v>5.947067259590415</v>
       </c>
       <c r="P22" t="n">
-        <v>390.8981310608851</v>
+        <v>390.9629685116957</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -38369,28 +38460,28 @@
         <v>0.0672</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1543705125051966</v>
+        <v>0.1485995237536964</v>
       </c>
       <c r="J23" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K23" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L23" t="n">
-        <v>0.02726571301107616</v>
+        <v>0.02526281761462301</v>
       </c>
       <c r="M23" t="n">
-        <v>5.180957724828112</v>
+        <v>5.195577107645307</v>
       </c>
       <c r="N23" t="n">
-        <v>48.21462020274139</v>
+        <v>48.4480232059771</v>
       </c>
       <c r="O23" t="n">
-        <v>6.943674834174004</v>
+        <v>6.960461421915727</v>
       </c>
       <c r="P23" t="n">
-        <v>390.2964753388245</v>
+        <v>390.3575504737776</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -38447,28 +38538,28 @@
         <v>0.0461</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1623220235865206</v>
+        <v>0.1561086088390535</v>
       </c>
       <c r="J24" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K24" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L24" t="n">
-        <v>0.02889809736005</v>
+        <v>0.02670845181655845</v>
       </c>
       <c r="M24" t="n">
-        <v>5.279211870176684</v>
+        <v>5.295606934814082</v>
       </c>
       <c r="N24" t="n">
-        <v>50.2138064843864</v>
+        <v>50.49907519337553</v>
       </c>
       <c r="O24" t="n">
-        <v>7.086170085764693</v>
+        <v>7.10627013231101</v>
       </c>
       <c r="P24" t="n">
-        <v>393.2700241014871</v>
+        <v>393.3357814890965</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -38506,7 +38597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y388"/>
+  <dimension ref="A1:Y389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87753,6 +87844,133 @@
         </is>
       </c>
     </row>
+    <row r="389">
+      <c r="A389" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>-36.78511340601062,175.06688537053682</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>-36.78533462408759,175.06774141219415</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>-36.7855230089507,175.06860829699562</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>-36.78575435376368,175.06946013856083</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>-36.78592601260451,175.07033142215195</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>-36.78609500817428,175.07120405893642</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>-36.7862372456075,175.07208455373265</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>-36.78638339287083,175.0729464214811</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>-36.786514610146405,175.0738101223906</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>-36.78663936944783,175.07469993477446</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>-36.78675859248767,175.07559233554875</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>-36.78685725342312,175.07648397169976</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>-36.78694313266988,175.07737028833296</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>-36.78704153852352,175.0782443346553</t>
+        </is>
+      </c>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>-36.787107558837825,175.07913084402716</t>
+        </is>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>-36.78717704071365,175.08002511881242</t>
+        </is>
+      </c>
+      <c r="R389" t="inlineStr">
+        <is>
+          <t>-36.7872549184919,175.0809171208208</t>
+        </is>
+      </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>-36.78731028383332,175.0818107385941</t>
+        </is>
+      </c>
+      <c r="T389" t="inlineStr">
+        <is>
+          <t>-36.78734197550797,175.08270765330863</t>
+        </is>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>-36.787402466237786,175.0836030028062</t>
+        </is>
+      </c>
+      <c r="V389" t="inlineStr">
+        <is>
+          <t>-36.78748025544967,175.08449821320377</t>
+        </is>
+      </c>
+      <c r="W389" t="inlineStr">
+        <is>
+          <t>-36.787533766259465,175.08540201080783</t>
+        </is>
+      </c>
+      <c r="X389" t="inlineStr">
+        <is>
+          <t>-36.787611974782365,175.0863021657307</t>
+        </is>
+      </c>
+      <c r="Y389" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0173/nzd0173.xlsx
+++ b/data/nzd0173/nzd0173.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y389"/>
+  <dimension ref="A1:Y390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31965,6 +31965,87 @@
         <v>384.88</v>
       </c>
       <c r="Y389" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>380.47</v>
+      </c>
+      <c r="C390" t="n">
+        <v>378.62</v>
+      </c>
+      <c r="D390" t="n">
+        <v>378.73</v>
+      </c>
+      <c r="E390" t="n">
+        <v>375.02</v>
+      </c>
+      <c r="F390" t="n">
+        <v>375.56</v>
+      </c>
+      <c r="G390" t="n">
+        <v>378.15</v>
+      </c>
+      <c r="H390" t="n">
+        <v>382.03</v>
+      </c>
+      <c r="I390" t="n">
+        <v>386.82</v>
+      </c>
+      <c r="J390" t="n">
+        <v>382.13</v>
+      </c>
+      <c r="K390" t="n">
+        <v>377.78</v>
+      </c>
+      <c r="L390" t="n">
+        <v>377.87</v>
+      </c>
+      <c r="M390" t="n">
+        <v>380.83</v>
+      </c>
+      <c r="N390" t="n">
+        <v>387.26</v>
+      </c>
+      <c r="O390" t="n">
+        <v>387.61</v>
+      </c>
+      <c r="P390" t="n">
+        <v>387.38</v>
+      </c>
+      <c r="Q390" t="n">
+        <v>385.72</v>
+      </c>
+      <c r="R390" t="n">
+        <v>384.84</v>
+      </c>
+      <c r="S390" t="n">
+        <v>384.4</v>
+      </c>
+      <c r="T390" t="n">
+        <v>386.77</v>
+      </c>
+      <c r="U390" t="n">
+        <v>386.03</v>
+      </c>
+      <c r="V390" t="n">
+        <v>383.88</v>
+      </c>
+      <c r="W390" t="n">
+        <v>384.18</v>
+      </c>
+      <c r="X390" t="n">
+        <v>387.62</v>
+      </c>
+      <c r="Y390" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -31981,7 +32062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B467"/>
+  <dimension ref="A1:B468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36654,6 +36735,16 @@
       </c>
       <c r="B467" t="n">
         <v>-0.68</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>-0.72</v>
       </c>
     </row>
   </sheetData>
@@ -36822,28 +36913,28 @@
         <v>0.078</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1099899689686221</v>
+        <v>0.1079844309743232</v>
       </c>
       <c r="J2" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K2" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0308447971105017</v>
+        <v>0.02986062890895314</v>
       </c>
       <c r="M2" t="n">
-        <v>3.470111505535109</v>
+        <v>3.471119055606381</v>
       </c>
       <c r="N2" t="n">
-        <v>21.61489114946995</v>
+        <v>21.60183284803461</v>
       </c>
       <c r="O2" t="n">
-        <v>4.649181772040103</v>
+        <v>4.647777194319303</v>
       </c>
       <c r="P2" t="n">
-        <v>381.6192362003546</v>
+        <v>381.6405897050171</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36900,28 +36991,28 @@
         <v>0.0623</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03336235470297361</v>
+        <v>0.03226094458338418</v>
       </c>
       <c r="J3" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K3" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003027371014764357</v>
+        <v>0.00284474405258861</v>
       </c>
       <c r="M3" t="n">
-        <v>3.321298154385288</v>
+        <v>3.31811795390703</v>
       </c>
       <c r="N3" t="n">
-        <v>20.754867783505</v>
+        <v>20.71433865078389</v>
       </c>
       <c r="O3" t="n">
-        <v>4.55575106689391</v>
+        <v>4.551300764702757</v>
       </c>
       <c r="P3" t="n">
-        <v>379.9727686777441</v>
+        <v>379.9845107579861</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36978,28 +37069,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0119109625005747</v>
+        <v>0.01012363610024112</v>
       </c>
       <c r="J4" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K4" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004364139124232169</v>
+        <v>0.0003164155010436653</v>
       </c>
       <c r="M4" t="n">
-        <v>3.108048587084206</v>
+        <v>3.108945998780091</v>
       </c>
       <c r="N4" t="n">
-        <v>18.39901390828885</v>
+        <v>18.38548921161289</v>
       </c>
       <c r="O4" t="n">
-        <v>4.289407174457661</v>
+        <v>4.287830361804544</v>
       </c>
       <c r="P4" t="n">
-        <v>382.0467370318892</v>
+        <v>382.0657916325671</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37056,28 +37147,28 @@
         <v>0.0529</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1260039614692125</v>
+        <v>0.1248323669032932</v>
       </c>
       <c r="J5" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K5" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03781631304122413</v>
+        <v>0.03731152802821269</v>
       </c>
       <c r="M5" t="n">
-        <v>3.647779950021959</v>
+        <v>3.643634823926253</v>
       </c>
       <c r="N5" t="n">
-        <v>22.87368821725551</v>
+        <v>22.82939883741671</v>
       </c>
       <c r="O5" t="n">
-        <v>4.782644479496203</v>
+        <v>4.778012017295134</v>
       </c>
       <c r="P5" t="n">
-        <v>374.0368706224659</v>
+        <v>374.0493609357102</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37134,28 +37225,28 @@
         <v>0.0608</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1373080551498483</v>
+        <v>0.1356372255603917</v>
       </c>
       <c r="J6" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K6" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05075249614364197</v>
+        <v>0.04976867885174374</v>
       </c>
       <c r="M6" t="n">
-        <v>3.237501181064756</v>
+        <v>3.236630579201431</v>
       </c>
       <c r="N6" t="n">
-        <v>19.96655238843507</v>
+        <v>19.94473883554115</v>
       </c>
       <c r="O6" t="n">
-        <v>4.468394833543146</v>
+        <v>4.465953295270915</v>
       </c>
       <c r="P6" t="n">
-        <v>375.2935122296606</v>
+        <v>375.311324863448</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37212,28 +37303,28 @@
         <v>0.0674</v>
       </c>
       <c r="I7" t="n">
-        <v>0.111178400044173</v>
+        <v>0.1102548317793474</v>
       </c>
       <c r="J7" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K7" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03480745100300775</v>
+        <v>0.03441342057299668</v>
       </c>
       <c r="M7" t="n">
-        <v>3.098936050755808</v>
+        <v>3.094906844904716</v>
       </c>
       <c r="N7" t="n">
-        <v>19.40758841697819</v>
+        <v>19.36671537379383</v>
       </c>
       <c r="O7" t="n">
-        <v>4.405404455549818</v>
+        <v>4.400763044495105</v>
       </c>
       <c r="P7" t="n">
-        <v>377.0583698454222</v>
+        <v>377.0682159622152</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37290,28 +37381,28 @@
         <v>0.0718</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1390559574322966</v>
+        <v>0.137840753920235</v>
       </c>
       <c r="J8" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K8" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05085160320853821</v>
+        <v>0.05022951467895709</v>
       </c>
       <c r="M8" t="n">
-        <v>3.243245837981795</v>
+        <v>3.239886998008084</v>
       </c>
       <c r="N8" t="n">
-        <v>20.43608318120838</v>
+        <v>20.39916056236364</v>
       </c>
       <c r="O8" t="n">
-        <v>4.520628626773978</v>
+        <v>4.516542987990221</v>
       </c>
       <c r="P8" t="n">
-        <v>380.7903553608615</v>
+        <v>380.8033105869806</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37368,28 +37459,28 @@
         <v>0.0609</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07192343767316778</v>
+        <v>0.07131588134185517</v>
       </c>
       <c r="J9" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K9" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01506002600261547</v>
+        <v>0.01488578346612379</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1024246762064</v>
+        <v>3.097724339318061</v>
       </c>
       <c r="N9" t="n">
-        <v>19.15640054906818</v>
+        <v>19.11105779470925</v>
       </c>
       <c r="O9" t="n">
-        <v>4.3768025485585</v>
+        <v>4.371619584857453</v>
       </c>
       <c r="P9" t="n">
-        <v>386.1335226539838</v>
+        <v>386.1399997827725</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37446,28 +37537,28 @@
         <v>0.1019</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08321899709504206</v>
+        <v>0.08208592727455848</v>
       </c>
       <c r="J10" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K10" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01964483081044599</v>
+        <v>0.01921131395550579</v>
       </c>
       <c r="M10" t="n">
-        <v>3.197381959197454</v>
+        <v>3.194897765815352</v>
       </c>
       <c r="N10" t="n">
-        <v>19.56902098960251</v>
+        <v>19.53228822098604</v>
       </c>
       <c r="O10" t="n">
-        <v>4.42368861806553</v>
+        <v>4.419534842150929</v>
       </c>
       <c r="P10" t="n">
-        <v>382.2126458815794</v>
+        <v>382.2247254843679</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37524,28 +37615,28 @@
         <v>0.0895</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1367171262107104</v>
+        <v>0.1353050604561552</v>
       </c>
       <c r="J11" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K11" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04710346598361204</v>
+        <v>0.04637304319591429</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25763882610016</v>
+        <v>3.255582485760348</v>
       </c>
       <c r="N11" t="n">
-        <v>21.4105447882842</v>
+        <v>21.37658521923408</v>
       </c>
       <c r="O11" t="n">
-        <v>4.627152989504907</v>
+        <v>4.623481936726267</v>
       </c>
       <c r="P11" t="n">
-        <v>376.9974682341063</v>
+        <v>377.0125221991118</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37602,28 +37693,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1534234160993966</v>
+        <v>0.1511409274576828</v>
       </c>
       <c r="J12" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K12" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07578003074006678</v>
+        <v>0.07384125831509958</v>
       </c>
       <c r="M12" t="n">
-        <v>2.906907672594703</v>
+        <v>2.909821987445493</v>
       </c>
       <c r="N12" t="n">
-        <v>16.25522035731352</v>
+        <v>16.2685121637068</v>
       </c>
       <c r="O12" t="n">
-        <v>4.031776327788227</v>
+        <v>4.033424371883871</v>
       </c>
       <c r="P12" t="n">
-        <v>378.4103817071321</v>
+        <v>378.4347152086187</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37680,28 +37771,28 @@
         <v>0.0849</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2254777141362868</v>
+        <v>0.2225151906353081</v>
       </c>
       <c r="J13" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K13" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1535103319573698</v>
+        <v>0.1500423341477045</v>
       </c>
       <c r="M13" t="n">
-        <v>2.840874592440692</v>
+        <v>2.848994537086656</v>
       </c>
       <c r="N13" t="n">
-        <v>15.87377758898001</v>
+        <v>15.92575909794782</v>
       </c>
       <c r="O13" t="n">
-        <v>3.98419095789597</v>
+        <v>3.990709097133969</v>
       </c>
       <c r="P13" t="n">
-        <v>380.829222188308</v>
+        <v>380.8608055086795</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37758,28 +37849,28 @@
         <v>0.0725</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1996974882238712</v>
+        <v>0.1970293277715782</v>
       </c>
       <c r="J14" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K14" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1052151430882647</v>
+        <v>0.1028414883307012</v>
       </c>
       <c r="M14" t="n">
-        <v>3.223447546231884</v>
+        <v>3.228663501113641</v>
       </c>
       <c r="N14" t="n">
-        <v>19.20324283193285</v>
+        <v>19.22914210977967</v>
       </c>
       <c r="O14" t="n">
-        <v>4.382150480293078</v>
+        <v>4.385104572274152</v>
       </c>
       <c r="P14" t="n">
-        <v>387.3493432040811</v>
+        <v>387.3777883341668</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37836,28 +37927,28 @@
         <v>0.0575</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1929099923638954</v>
+        <v>0.1892598346939786</v>
       </c>
       <c r="J15" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K15" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1009317820129122</v>
+        <v>0.0973291649537994</v>
       </c>
       <c r="M15" t="n">
-        <v>3.138722904712612</v>
+        <v>3.151729392489372</v>
       </c>
       <c r="N15" t="n">
-        <v>18.76995129882493</v>
+        <v>18.86256092400757</v>
       </c>
       <c r="O15" t="n">
-        <v>4.332430183952758</v>
+        <v>4.343104986528367</v>
       </c>
       <c r="P15" t="n">
-        <v>389.8864758219663</v>
+        <v>389.9253899770969</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -37914,28 +38005,28 @@
         <v>0.0631</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2074883577446348</v>
+        <v>0.2045073107196877</v>
       </c>
       <c r="J16" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K16" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1071178214635822</v>
+        <v>0.1044493071925333</v>
       </c>
       <c r="M16" t="n">
-        <v>3.263700171670611</v>
+        <v>3.271738991653073</v>
       </c>
       <c r="N16" t="n">
-        <v>20.31930659334192</v>
+        <v>20.36102397204519</v>
       </c>
       <c r="O16" t="n">
-        <v>4.507694154813736</v>
+        <v>4.512319134552119</v>
       </c>
       <c r="P16" t="n">
-        <v>387.8980316174463</v>
+        <v>387.9298124162147</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -37992,28 +38083,28 @@
         <v>0.068</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1666007758064643</v>
+        <v>0.1631250170674046</v>
       </c>
       <c r="J17" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K17" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L17" t="n">
-        <v>0.07750625499383856</v>
+        <v>0.07444348070765572</v>
       </c>
       <c r="M17" t="n">
-        <v>3.077618305836726</v>
+        <v>3.090626232056378</v>
       </c>
       <c r="N17" t="n">
-        <v>18.70551672239434</v>
+        <v>18.78515325941044</v>
       </c>
       <c r="O17" t="n">
-        <v>4.324987482339613</v>
+        <v>4.334184266896187</v>
       </c>
       <c r="P17" t="n">
-        <v>388.3374927137199</v>
+        <v>388.3745476102476</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -38070,28 +38161,28 @@
         <v>0.0687</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1682734227760594</v>
+        <v>0.1645386443286829</v>
       </c>
       <c r="J18" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K18" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L18" t="n">
-        <v>0.06890715577504014</v>
+        <v>0.06599311705285282</v>
       </c>
       <c r="M18" t="n">
-        <v>3.358570760382905</v>
+        <v>3.369780487852021</v>
       </c>
       <c r="N18" t="n">
-        <v>21.66450225139452</v>
+        <v>21.75627769334113</v>
       </c>
       <c r="O18" t="n">
-        <v>4.654514179954178</v>
+        <v>4.664362517358737</v>
       </c>
       <c r="P18" t="n">
-        <v>387.9476289332763</v>
+        <v>387.9874452264401</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -38148,28 +38239,28 @@
         <v>0.0696</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2072827910395877</v>
+        <v>0.2029158820031018</v>
       </c>
       <c r="J19" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K19" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L19" t="n">
-        <v>0.08227655965542047</v>
+        <v>0.07896744907776088</v>
       </c>
       <c r="M19" t="n">
-        <v>4.017314459480431</v>
+        <v>4.029571427765185</v>
       </c>
       <c r="N19" t="n">
-        <v>27.13633486766746</v>
+        <v>27.26818800087562</v>
       </c>
       <c r="O19" t="n">
-        <v>5.209254732461013</v>
+        <v>5.221895058393612</v>
       </c>
       <c r="P19" t="n">
-        <v>387.7439168824509</v>
+        <v>387.7904722893824</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -38226,28 +38317,28 @@
         <v>0.0623</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2424127058973381</v>
+        <v>0.2386078906187906</v>
       </c>
       <c r="J20" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K20" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L20" t="n">
-        <v>0.102992490986245</v>
+        <v>0.1001126953262563</v>
       </c>
       <c r="M20" t="n">
-        <v>4.0097211449269</v>
+        <v>4.021391000944507</v>
       </c>
       <c r="N20" t="n">
-        <v>28.97945866811274</v>
+        <v>29.05801228173695</v>
       </c>
       <c r="O20" t="n">
-        <v>5.383257254498687</v>
+        <v>5.390548421240362</v>
       </c>
       <c r="P20" t="n">
-        <v>388.036244013157</v>
+        <v>388.0768069656052</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -38304,28 +38395,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.07243453308328489</v>
+        <v>0.06903224214076623</v>
       </c>
       <c r="J21" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K21" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01016807709817569</v>
+        <v>0.009254220183934403</v>
       </c>
       <c r="M21" t="n">
-        <v>4.048420067687102</v>
+        <v>4.055851388770071</v>
       </c>
       <c r="N21" t="n">
-        <v>28.92031033935304</v>
+        <v>28.96834543127924</v>
       </c>
       <c r="O21" t="n">
-        <v>5.37776071793391</v>
+        <v>5.382224951753618</v>
       </c>
       <c r="P21" t="n">
-        <v>391.0199796514274</v>
+        <v>391.0562513113143</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -38382,28 +38473,28 @@
         <v>0.0607</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1320897521270053</v>
+        <v>0.1268789956153918</v>
       </c>
       <c r="J22" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K22" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02728681415700585</v>
+        <v>0.0251606335004515</v>
       </c>
       <c r="M22" t="n">
-        <v>4.408005933017304</v>
+        <v>4.424592014498064</v>
       </c>
       <c r="N22" t="n">
-        <v>35.36760899009226</v>
+        <v>35.56510414517228</v>
       </c>
       <c r="O22" t="n">
-        <v>5.947067259590415</v>
+        <v>5.963648559830826</v>
       </c>
       <c r="P22" t="n">
-        <v>390.9629685116957</v>
+        <v>391.018448843548</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -38460,28 +38551,28 @@
         <v>0.0672</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1485995237536964</v>
+        <v>0.1436152476906762</v>
       </c>
       <c r="J23" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K23" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L23" t="n">
-        <v>0.02526281761462301</v>
+        <v>0.02363337336470184</v>
       </c>
       <c r="M23" t="n">
-        <v>5.195577107645307</v>
+        <v>5.206034247517562</v>
       </c>
       <c r="N23" t="n">
-        <v>48.4480232059771</v>
+        <v>48.58715242788725</v>
       </c>
       <c r="O23" t="n">
-        <v>6.960461421915727</v>
+        <v>6.970448509808192</v>
       </c>
       <c r="P23" t="n">
-        <v>390.3575504737776</v>
+        <v>390.4106194071279</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -38538,28 +38629,28 @@
         <v>0.0461</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1561086088390535</v>
+        <v>0.1512561056328471</v>
       </c>
       <c r="J24" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K24" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L24" t="n">
-        <v>0.02670845181655845</v>
+        <v>0.02512428326873495</v>
       </c>
       <c r="M24" t="n">
-        <v>5.295606934814082</v>
+        <v>5.305121792306058</v>
       </c>
       <c r="N24" t="n">
-        <v>50.49907519337553</v>
+        <v>50.61911336317968</v>
       </c>
       <c r="O24" t="n">
-        <v>7.10627013231101</v>
+        <v>7.114711052683705</v>
       </c>
       <c r="P24" t="n">
-        <v>393.3357814890965</v>
+        <v>393.3874474012523</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -38597,7 +38688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y389"/>
+  <dimension ref="A1:Y390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87971,6 +88062,133 @@
         </is>
       </c>
     </row>
+    <row r="390">
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>-36.78511453817297,175.06688499663272</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>-36.785324870061906,175.06774463345792</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>-36.78551813193195,175.06860990759463</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>-36.785744499025,175.06946332412042</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>-36.78592653667744,175.07033125694153</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>-36.78608967683497,175.07120572248002</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>-36.78623917018421,175.0720839627498</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>-36.78637506147119,175.07294832075277</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>-36.78651272964346,175.07381038467895</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>-36.78663436500932,175.07470073957427</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>-36.78675610307752,175.0755928461848</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>-36.78686195988533,175.07648296360188</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>-36.7869360926298,175.07737159990083</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>-36.78703257259015,175.07824545289523</t>
+        </is>
+      </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>-36.78709686449954,175.07913181825714</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>-36.78717443453019,175.0800253562101</t>
+        </is>
+      </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>-36.78724493915482,175.0809179597847</t>
+        </is>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>-36.787303447845005,175.08181124890714</t>
+        </is>
+      </c>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>-36.78733396929481,175.08270823167518</t>
+        </is>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>-36.787392480960875,175.08360372406392</t>
+        </is>
+      </c>
+      <c r="V390" t="inlineStr">
+        <is>
+          <t>-36.78746370772093,175.0844995002188</t>
+        </is>
+      </c>
+      <c r="W390" t="inlineStr">
+        <is>
+          <t>-36.78751959304098,175.0854036874873</t>
+        </is>
+      </c>
+      <c r="X390" t="inlineStr">
+        <is>
+          <t>-36.78758747082304,175.08630592570844</t>
+        </is>
+      </c>
+      <c r="Y390" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0173/nzd0173.xlsx
+++ b/data/nzd0173/nzd0173.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y390"/>
+  <dimension ref="A1:Y394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32048,6 +32048,330 @@
       <c r="Y390" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>380.47</v>
+      </c>
+      <c r="C391" t="n">
+        <v>378.62</v>
+      </c>
+      <c r="D391" t="n">
+        <v>378.73</v>
+      </c>
+      <c r="E391" t="n">
+        <v>375.02</v>
+      </c>
+      <c r="F391" t="n">
+        <v>375.56</v>
+      </c>
+      <c r="G391" t="n">
+        <v>378.15</v>
+      </c>
+      <c r="H391" t="n">
+        <v>382.03</v>
+      </c>
+      <c r="I391" t="n">
+        <v>390.48</v>
+      </c>
+      <c r="J391" t="n">
+        <v>382.97</v>
+      </c>
+      <c r="K391" t="n">
+        <v>378.01</v>
+      </c>
+      <c r="L391" t="n">
+        <v>377.74</v>
+      </c>
+      <c r="M391" t="n">
+        <v>381.18</v>
+      </c>
+      <c r="N391" t="n">
+        <v>387.82</v>
+      </c>
+      <c r="O391" t="n">
+        <v>388.53</v>
+      </c>
+      <c r="P391" t="n">
+        <v>387.43</v>
+      </c>
+      <c r="Q391" t="n">
+        <v>386.14</v>
+      </c>
+      <c r="R391" t="n">
+        <v>385.29</v>
+      </c>
+      <c r="S391" t="n">
+        <v>385.02</v>
+      </c>
+      <c r="T391" t="n">
+        <v>386.84</v>
+      </c>
+      <c r="U391" t="n">
+        <v>385.94</v>
+      </c>
+      <c r="V391" t="n">
+        <v>383.94</v>
+      </c>
+      <c r="W391" t="n">
+        <v>384.07</v>
+      </c>
+      <c r="X391" t="n">
+        <v>387.5</v>
+      </c>
+      <c r="Y391" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>381.98</v>
+      </c>
+      <c r="C392" t="n">
+        <v>379.31</v>
+      </c>
+      <c r="D392" t="n">
+        <v>378.84</v>
+      </c>
+      <c r="E392" t="n">
+        <v>375.94</v>
+      </c>
+      <c r="F392" t="n">
+        <v>376.16</v>
+      </c>
+      <c r="G392" t="n">
+        <v>378.24</v>
+      </c>
+      <c r="H392" t="n">
+        <v>381.88</v>
+      </c>
+      <c r="I392" t="n">
+        <v>391.31</v>
+      </c>
+      <c r="J392" t="n">
+        <v>387.34</v>
+      </c>
+      <c r="K392" t="n">
+        <v>378.75</v>
+      </c>
+      <c r="L392" t="n">
+        <v>377.68</v>
+      </c>
+      <c r="M392" t="n">
+        <v>381.48</v>
+      </c>
+      <c r="N392" t="n">
+        <v>388.54</v>
+      </c>
+      <c r="O392" t="n">
+        <v>389.17</v>
+      </c>
+      <c r="P392" t="n">
+        <v>387.98</v>
+      </c>
+      <c r="Q392" t="n">
+        <v>386.85</v>
+      </c>
+      <c r="R392" t="n">
+        <v>386.14</v>
+      </c>
+      <c r="S392" t="n">
+        <v>386.27</v>
+      </c>
+      <c r="T392" t="n">
+        <v>388.1</v>
+      </c>
+      <c r="U392" t="n">
+        <v>386.89</v>
+      </c>
+      <c r="V392" t="n">
+        <v>385.1</v>
+      </c>
+      <c r="W392" t="n">
+        <v>385.38</v>
+      </c>
+      <c r="X392" t="n">
+        <v>388.2</v>
+      </c>
+      <c r="Y392" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>381.61</v>
+      </c>
+      <c r="C393" t="n">
+        <v>378.83</v>
+      </c>
+      <c r="D393" t="n">
+        <v>378.75</v>
+      </c>
+      <c r="E393" t="n">
+        <v>375.56</v>
+      </c>
+      <c r="F393" t="n">
+        <v>376.57</v>
+      </c>
+      <c r="G393" t="n">
+        <v>377.98</v>
+      </c>
+      <c r="H393" t="n">
+        <v>382.32</v>
+      </c>
+      <c r="I393" t="n">
+        <v>390.82</v>
+      </c>
+      <c r="J393" t="n">
+        <v>387.11</v>
+      </c>
+      <c r="K393" t="n">
+        <v>378.43</v>
+      </c>
+      <c r="L393" t="n">
+        <v>377.9</v>
+      </c>
+      <c r="M393" t="n">
+        <v>382.16</v>
+      </c>
+      <c r="N393" t="n">
+        <v>389.61</v>
+      </c>
+      <c r="O393" t="n">
+        <v>389.12</v>
+      </c>
+      <c r="P393" t="n">
+        <v>388.29</v>
+      </c>
+      <c r="Q393" t="n">
+        <v>387.42</v>
+      </c>
+      <c r="R393" t="n">
+        <v>386.98</v>
+      </c>
+      <c r="S393" t="n">
+        <v>385.98</v>
+      </c>
+      <c r="T393" t="n">
+        <v>387.66</v>
+      </c>
+      <c r="U393" t="n">
+        <v>386.55</v>
+      </c>
+      <c r="V393" t="n">
+        <v>385.3</v>
+      </c>
+      <c r="W393" t="n">
+        <v>385.52</v>
+      </c>
+      <c r="X393" t="n">
+        <v>387.45</v>
+      </c>
+      <c r="Y393" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>383.11</v>
+      </c>
+      <c r="C394" t="n">
+        <v>380.54</v>
+      </c>
+      <c r="D394" t="n">
+        <v>379.78</v>
+      </c>
+      <c r="E394" t="n">
+        <v>377.11</v>
+      </c>
+      <c r="F394" t="n">
+        <v>377.4</v>
+      </c>
+      <c r="G394" t="n">
+        <v>378.32</v>
+      </c>
+      <c r="H394" t="n">
+        <v>382.9</v>
+      </c>
+      <c r="I394" t="n">
+        <v>390.45</v>
+      </c>
+      <c r="J394" t="n">
+        <v>387.09</v>
+      </c>
+      <c r="K394" t="n">
+        <v>378.69</v>
+      </c>
+      <c r="L394" t="n">
+        <v>378.19</v>
+      </c>
+      <c r="M394" t="n">
+        <v>382.1</v>
+      </c>
+      <c r="N394" t="n">
+        <v>389.76</v>
+      </c>
+      <c r="O394" t="n">
+        <v>389.49</v>
+      </c>
+      <c r="P394" t="n">
+        <v>388.62</v>
+      </c>
+      <c r="Q394" t="n">
+        <v>387.92</v>
+      </c>
+      <c r="R394" t="n">
+        <v>387.28</v>
+      </c>
+      <c r="S394" t="n">
+        <v>387.23</v>
+      </c>
+      <c r="T394" t="n">
+        <v>388.81</v>
+      </c>
+      <c r="U394" t="n">
+        <v>387.45</v>
+      </c>
+      <c r="V394" t="n">
+        <v>386.51</v>
+      </c>
+      <c r="W394" t="n">
+        <v>387.05</v>
+      </c>
+      <c r="X394" t="n">
+        <v>388.6</v>
+      </c>
+      <c r="Y394" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -32062,7 +32386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B468"/>
+  <dimension ref="A1:B472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36745,6 +37069,46 @@
       </c>
       <c r="B468" t="n">
         <v>-0.72</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>-0.84</v>
       </c>
     </row>
   </sheetData>
@@ -36913,28 +37277,28 @@
         <v>0.078</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1079844309743232</v>
+        <v>0.1027313318843556</v>
       </c>
       <c r="J2" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K2" t="n">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02986062890895314</v>
+        <v>0.02756070107970698</v>
       </c>
       <c r="M2" t="n">
-        <v>3.471119055606381</v>
+        <v>3.461870315125364</v>
       </c>
       <c r="N2" t="n">
-        <v>21.60183284803461</v>
+        <v>21.4644517262283</v>
       </c>
       <c r="O2" t="n">
-        <v>4.647777194319303</v>
+        <v>4.632974393003732</v>
       </c>
       <c r="P2" t="n">
-        <v>381.6405897050171</v>
+        <v>381.6966957148853</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36991,28 +37355,28 @@
         <v>0.0623</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03226094458338418</v>
+        <v>0.02934059372502025</v>
       </c>
       <c r="J3" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K3" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00284474405258861</v>
+        <v>0.002401099062803391</v>
       </c>
       <c r="M3" t="n">
-        <v>3.31811795390703</v>
+        <v>3.298327680734662</v>
       </c>
       <c r="N3" t="n">
-        <v>20.71433865078389</v>
+        <v>20.53203267970853</v>
       </c>
       <c r="O3" t="n">
-        <v>4.551300764702757</v>
+        <v>4.531228605986298</v>
       </c>
       <c r="P3" t="n">
-        <v>379.9845107579861</v>
+        <v>380.0157381612002</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37069,28 +37433,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01012363610024112</v>
+        <v>0.003774951149360269</v>
       </c>
       <c r="J4" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K4" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003164155010436653</v>
+        <v>4.467846533873221e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.108945998780091</v>
+        <v>3.108785779516717</v>
       </c>
       <c r="N4" t="n">
-        <v>18.38548921161289</v>
+        <v>18.30852207843714</v>
       </c>
       <c r="O4" t="n">
-        <v>4.287830361804544</v>
+        <v>4.278845881594375</v>
       </c>
       <c r="P4" t="n">
-        <v>382.0657916325671</v>
+        <v>382.1336998995444</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37147,28 +37511,28 @@
         <v>0.0529</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1248323669032932</v>
+        <v>0.1219750594535075</v>
       </c>
       <c r="J5" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K5" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03731152802821269</v>
+        <v>0.03637567566288347</v>
       </c>
       <c r="M5" t="n">
-        <v>3.643634823926253</v>
+        <v>3.619213811401648</v>
       </c>
       <c r="N5" t="n">
-        <v>22.82939883741671</v>
+        <v>22.62491882187418</v>
       </c>
       <c r="O5" t="n">
-        <v>4.778012017295134</v>
+        <v>4.756565864347321</v>
       </c>
       <c r="P5" t="n">
-        <v>374.0493609357102</v>
+        <v>374.0799124162498</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37225,28 +37589,28 @@
         <v>0.0608</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1356372255603917</v>
+        <v>0.1307984322161118</v>
       </c>
       <c r="J6" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K6" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04976867885174374</v>
+        <v>0.0472359720065948</v>
       </c>
       <c r="M6" t="n">
-        <v>3.236630579201431</v>
+        <v>3.225236537945479</v>
       </c>
       <c r="N6" t="n">
-        <v>19.94473883554115</v>
+        <v>19.80914995453526</v>
       </c>
       <c r="O6" t="n">
-        <v>4.465953295270915</v>
+        <v>4.450747123184517</v>
       </c>
       <c r="P6" t="n">
-        <v>375.311324863448</v>
+        <v>375.3630735105409</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37303,28 +37667,28 @@
         <v>0.0674</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1102548317793474</v>
+        <v>0.1067029658506356</v>
       </c>
       <c r="J7" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K7" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03441342057299668</v>
+        <v>0.03291420074887041</v>
       </c>
       <c r="M7" t="n">
-        <v>3.094906844904716</v>
+        <v>3.078319156895281</v>
       </c>
       <c r="N7" t="n">
-        <v>19.36671537379383</v>
+        <v>19.20361284929567</v>
       </c>
       <c r="O7" t="n">
-        <v>4.400763044495105</v>
+        <v>4.382192698786268</v>
       </c>
       <c r="P7" t="n">
-        <v>377.0682159622152</v>
+        <v>377.1062121405965</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37381,28 +37745,28 @@
         <v>0.0718</v>
       </c>
       <c r="I8" t="n">
-        <v>0.137840753920235</v>
+        <v>0.1335924731134103</v>
       </c>
       <c r="J8" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K8" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05022951467895709</v>
+        <v>0.04817548698953911</v>
       </c>
       <c r="M8" t="n">
-        <v>3.239886998008084</v>
+        <v>3.224412909796259</v>
       </c>
       <c r="N8" t="n">
-        <v>20.39916056236364</v>
+        <v>20.24151518997616</v>
       </c>
       <c r="O8" t="n">
-        <v>4.516542987990221</v>
+        <v>4.49905714455553</v>
       </c>
       <c r="P8" t="n">
-        <v>380.8033105869806</v>
+        <v>380.8487495778583</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37459,28 +37823,28 @@
         <v>0.0609</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07131588134185517</v>
+        <v>0.07651845651658037</v>
       </c>
       <c r="J9" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K9" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01488578346612379</v>
+        <v>0.01739112274253751</v>
       </c>
       <c r="M9" t="n">
-        <v>3.097724339318061</v>
+        <v>3.092579237604812</v>
       </c>
       <c r="N9" t="n">
-        <v>19.11105779470925</v>
+        <v>18.99038339792362</v>
       </c>
       <c r="O9" t="n">
-        <v>4.371619584857453</v>
+        <v>4.357795704014086</v>
       </c>
       <c r="P9" t="n">
-        <v>386.1399997827725</v>
+        <v>386.0843458573083</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37537,28 +37901,28 @@
         <v>0.1019</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08208592727455848</v>
+        <v>0.08535286107935745</v>
       </c>
       <c r="J10" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K10" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01921131395550579</v>
+        <v>0.02110627855853975</v>
       </c>
       <c r="M10" t="n">
-        <v>3.194897765815352</v>
+        <v>3.187391330998574</v>
       </c>
       <c r="N10" t="n">
-        <v>19.53228822098604</v>
+        <v>19.3958274474444</v>
       </c>
       <c r="O10" t="n">
-        <v>4.419534842150929</v>
+        <v>4.404069419008334</v>
       </c>
       <c r="P10" t="n">
-        <v>382.2247254843679</v>
+        <v>382.1897457033079</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37615,28 +37979,28 @@
         <v>0.0895</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1353050604561552</v>
+        <v>0.1311356452178273</v>
       </c>
       <c r="J11" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K11" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04637304319591429</v>
+        <v>0.04447953990932696</v>
       </c>
       <c r="M11" t="n">
-        <v>3.255582485760348</v>
+        <v>3.240979339336802</v>
       </c>
       <c r="N11" t="n">
-        <v>21.37658521923408</v>
+        <v>21.20652392382318</v>
       </c>
       <c r="O11" t="n">
-        <v>4.623481936726267</v>
+        <v>4.605054171649144</v>
       </c>
       <c r="P11" t="n">
-        <v>377.0125221991118</v>
+        <v>377.0571209066737</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37693,28 +38057,28 @@
         <v>0.07190000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1511409274576828</v>
+        <v>0.1423017645375866</v>
       </c>
       <c r="J12" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K12" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07384125831509958</v>
+        <v>0.06651832509379751</v>
       </c>
       <c r="M12" t="n">
-        <v>2.909821987445493</v>
+        <v>2.921957629588176</v>
       </c>
       <c r="N12" t="n">
-        <v>16.2685121637068</v>
+        <v>16.31298097176062</v>
       </c>
       <c r="O12" t="n">
-        <v>4.033424371883871</v>
+        <v>4.038933147721143</v>
       </c>
       <c r="P12" t="n">
-        <v>378.4347152086187</v>
+        <v>378.5292697309018</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37771,28 +38135,28 @@
         <v>0.0849</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2225151906353081</v>
+        <v>0.2127483289870119</v>
       </c>
       <c r="J13" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K13" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1500423341477045</v>
+        <v>0.1395433315909077</v>
       </c>
       <c r="M13" t="n">
-        <v>2.848994537086656</v>
+        <v>2.870535238886069</v>
       </c>
       <c r="N13" t="n">
-        <v>15.92575909794782</v>
+        <v>16.02140134382374</v>
       </c>
       <c r="O13" t="n">
-        <v>3.990709097133969</v>
+        <v>4.002674274010282</v>
       </c>
       <c r="P13" t="n">
-        <v>380.8608055086795</v>
+        <v>380.9652795037838</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37849,28 +38213,28 @@
         <v>0.0725</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1970293277715782</v>
+        <v>0.1898825820572446</v>
       </c>
       <c r="J14" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K14" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1028414883307012</v>
+        <v>0.09741536973707055</v>
       </c>
       <c r="M14" t="n">
-        <v>3.228663501113641</v>
+        <v>3.231809536394891</v>
       </c>
       <c r="N14" t="n">
-        <v>19.22914210977967</v>
+        <v>19.1769252515524</v>
       </c>
       <c r="O14" t="n">
-        <v>4.385104572274152</v>
+        <v>4.379146635082273</v>
       </c>
       <c r="P14" t="n">
-        <v>387.3777883341668</v>
+        <v>387.4542243353918</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37927,28 +38291,28 @@
         <v>0.0575</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1892598346939786</v>
+        <v>0.1778995982512324</v>
       </c>
       <c r="J15" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K15" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0973291649537994</v>
+        <v>0.08719809884434782</v>
       </c>
       <c r="M15" t="n">
-        <v>3.151729392489372</v>
+        <v>3.186540256681039</v>
       </c>
       <c r="N15" t="n">
-        <v>18.86256092400757</v>
+        <v>19.01812606153386</v>
       </c>
       <c r="O15" t="n">
-        <v>4.343104986528367</v>
+        <v>4.360977649740235</v>
       </c>
       <c r="P15" t="n">
-        <v>389.9253899770969</v>
+        <v>390.0469108852656</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -38005,28 +38369,28 @@
         <v>0.0631</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2045073107196877</v>
+        <v>0.1942810771474162</v>
       </c>
       <c r="J16" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K16" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1044493071925333</v>
+        <v>0.09586075159042129</v>
       </c>
       <c r="M16" t="n">
-        <v>3.271738991653073</v>
+        <v>3.294764980771025</v>
       </c>
       <c r="N16" t="n">
-        <v>20.36102397204519</v>
+        <v>20.43637038994072</v>
       </c>
       <c r="O16" t="n">
-        <v>4.512319134552119</v>
+        <v>4.520660393121863</v>
       </c>
       <c r="P16" t="n">
-        <v>387.9298124162147</v>
+        <v>388.0391995258771</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -38083,28 +38447,28 @@
         <v>0.068</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1631250170674046</v>
+        <v>0.1522570105244818</v>
       </c>
       <c r="J17" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K17" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L17" t="n">
-        <v>0.07444348070765572</v>
+        <v>0.06572921016651023</v>
       </c>
       <c r="M17" t="n">
-        <v>3.090626232056378</v>
+        <v>3.126451616357415</v>
       </c>
       <c r="N17" t="n">
-        <v>18.78515325941044</v>
+        <v>18.91547368369379</v>
       </c>
       <c r="O17" t="n">
-        <v>4.334184266896187</v>
+        <v>4.349192302450398</v>
       </c>
       <c r="P17" t="n">
-        <v>388.3745476102476</v>
+        <v>388.490794858726</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -38161,28 +38525,28 @@
         <v>0.0687</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1645386443286829</v>
+        <v>0.1530774214229261</v>
       </c>
       <c r="J18" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K18" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L18" t="n">
-        <v>0.06599311705285282</v>
+        <v>0.05788392554822097</v>
       </c>
       <c r="M18" t="n">
-        <v>3.369780487852021</v>
+        <v>3.396841161623013</v>
       </c>
       <c r="N18" t="n">
-        <v>21.75627769334113</v>
+        <v>21.89359000524403</v>
       </c>
       <c r="O18" t="n">
-        <v>4.664362517358737</v>
+        <v>4.679058666574297</v>
       </c>
       <c r="P18" t="n">
-        <v>387.9874452264401</v>
+        <v>388.1100361842996</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -38239,28 +38603,28 @@
         <v>0.0696</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2029158820031018</v>
+        <v>0.1892909471597568</v>
       </c>
       <c r="J19" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K19" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L19" t="n">
-        <v>0.07896744907776088</v>
+        <v>0.06960174305144129</v>
       </c>
       <c r="M19" t="n">
-        <v>4.029571427765185</v>
+        <v>4.060302257464422</v>
       </c>
       <c r="N19" t="n">
-        <v>27.26818800087562</v>
+        <v>27.49519020057643</v>
       </c>
       <c r="O19" t="n">
-        <v>5.221895058393612</v>
+        <v>5.243585624415457</v>
       </c>
       <c r="P19" t="n">
-        <v>387.7904722893824</v>
+        <v>387.9362112410881</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -38317,28 +38681,28 @@
         <v>0.0623</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2386078906187906</v>
+        <v>0.2259125082671806</v>
       </c>
       <c r="J20" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K20" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1001126953262563</v>
+        <v>0.09118462128129767</v>
       </c>
       <c r="M20" t="n">
-        <v>4.021391000944507</v>
+        <v>4.05414970862435</v>
       </c>
       <c r="N20" t="n">
-        <v>29.05801228173695</v>
+        <v>29.20000267138147</v>
       </c>
       <c r="O20" t="n">
-        <v>5.390548421240362</v>
+        <v>5.403702681623173</v>
       </c>
       <c r="P20" t="n">
-        <v>388.0768069656052</v>
+        <v>388.212604088973</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -38395,28 +38759,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.06903224214076623</v>
+        <v>0.05714761608520733</v>
       </c>
       <c r="J21" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K21" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L21" t="n">
-        <v>0.009254220183934403</v>
+        <v>0.006410923227852861</v>
       </c>
       <c r="M21" t="n">
-        <v>4.055851388770071</v>
+        <v>4.077373285519432</v>
       </c>
       <c r="N21" t="n">
-        <v>28.96834543127924</v>
+        <v>29.05565944752409</v>
       </c>
       <c r="O21" t="n">
-        <v>5.382224951753618</v>
+        <v>5.390330179824246</v>
       </c>
       <c r="P21" t="n">
-        <v>391.0562513113143</v>
+        <v>391.183378398819</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -38473,28 +38837,28 @@
         <v>0.0607</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1268789956153918</v>
+        <v>0.1092370053549028</v>
       </c>
       <c r="J22" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K22" t="n">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0251606335004515</v>
+        <v>0.0187224405464288</v>
       </c>
       <c r="M22" t="n">
-        <v>4.424592014498064</v>
+        <v>4.47486998371796</v>
       </c>
       <c r="N22" t="n">
-        <v>35.56510414517228</v>
+        <v>36.05045083320478</v>
       </c>
       <c r="O22" t="n">
-        <v>5.963648559830826</v>
+        <v>6.004202764164846</v>
       </c>
       <c r="P22" t="n">
-        <v>391.018448843548</v>
+        <v>391.206920033535</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -38551,28 +38915,28 @@
         <v>0.0672</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1436152476906762</v>
+        <v>0.1268402908615539</v>
       </c>
       <c r="J23" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K23" t="n">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="L23" t="n">
-        <v>0.02363337336470184</v>
+        <v>0.01862613006729097</v>
       </c>
       <c r="M23" t="n">
-        <v>5.206034247517562</v>
+        <v>5.235694696144046</v>
       </c>
       <c r="N23" t="n">
-        <v>48.58715242788725</v>
+        <v>48.86163993146224</v>
       </c>
       <c r="O23" t="n">
-        <v>6.970448509808192</v>
+        <v>6.990110151597201</v>
       </c>
       <c r="P23" t="n">
-        <v>390.4106194071279</v>
+        <v>390.5898239428189</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -38629,28 +38993,28 @@
         <v>0.0461</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1512561056328471</v>
+        <v>0.1330407687433801</v>
       </c>
       <c r="J24" t="n">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="K24" t="n">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="L24" t="n">
-        <v>0.02512428326873495</v>
+        <v>0.01961290103135127</v>
       </c>
       <c r="M24" t="n">
-        <v>5.305121792306058</v>
+        <v>5.337203193357163</v>
       </c>
       <c r="N24" t="n">
-        <v>50.61911336317968</v>
+        <v>50.99962277134744</v>
       </c>
       <c r="O24" t="n">
-        <v>7.114711052683705</v>
+        <v>7.141402017205546</v>
       </c>
       <c r="P24" t="n">
-        <v>393.3874474012523</v>
+        <v>393.5820582965007</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -38688,7 +39052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y390"/>
+  <dimension ref="A1:Y394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88189,6 +88553,514 @@
         </is>
       </c>
     </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>-36.78511453817297,175.06688499663272</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>-36.785324870061906,175.06774463345792</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>-36.78551813193195,175.06860990759463</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>-36.785744499025,175.06946332412042</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>-36.78592653667744,175.07033125694153</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>-36.78608967683497,175.07120572248002</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>-36.78623917018421,175.0720839627498</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>-36.78634262219146,175.07295571578578</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>-36.78650520763171,175.07381143383228</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>-36.78663230961492,175.07470107011702</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>-36.7867572588751,175.07559260910378</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>-36.78685885184425,175.0764836293269</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>-36.78693110222165,175.0773725296197</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>-36.78702432393144,175.07824648167582</t>
+        </is>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>-36.787096415157585,175.07913185919116</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>-36.78717066005757,175.08002570002742</t>
+        </is>
+      </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>-36.78724089347761,175.08091829990516</t>
+        </is>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>-36.78729787111769,175.0818116652151</t>
+        </is>
+      </c>
+      <c r="T391" t="inlineStr">
+        <is>
+          <t>-36.78733333959264,175.0827082771647</t>
+        </is>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>-36.78739329057792,175.08360366558355</t>
+        </is>
+      </c>
+      <c r="V391" t="inlineStr">
+        <is>
+          <t>-36.78746316812108,175.0844995421867</t>
+        </is>
+      </c>
+      <c r="W391" t="inlineStr">
+        <is>
+          <t>-36.78752057978405,175.08540357075645</t>
+        </is>
+      </c>
+      <c r="X391" t="inlineStr">
+        <is>
+          <t>-36.78758854398915,175.08630576103792</t>
+        </is>
+      </c>
+      <c r="Y391" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>-36.78510138767179,175.066889339672</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>-36.78531886088533,175.06774661798613</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>-36.78551717394611,175.06861022396228</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>-36.785736475697895,175.0694659176728</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>-36.78592129594818,175.07033290904567</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>-36.78608889024393,175.0712059679209</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>-36.78624048239559,175.0720835598069</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>-36.786335265742714,175.07295739280065</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>-36.78646607526088,175.0738168919247</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>-36.78662569660686,175.07470213360227</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>-36.78675779232011,175.07559249968176</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>-36.786856187809036,175.07648419994834</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>-36.7869246859826,175.0773737249724</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>-36.787018585734074,175.07824719734919</t>
+        </is>
+      </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>-36.78709147239619,175.07913230946545</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>-36.78716427940148,175.0800262812423</t>
+        </is>
+      </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>-36.7872332516429,175.0809189423548</t>
+        </is>
+      </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>-36.78728662771582,175.08181250454555</t>
+        </is>
+      </c>
+      <c r="T392" t="inlineStr">
+        <is>
+          <t>-36.78732200495376,175.08270909597562</t>
+        </is>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>-36.78738474462019,175.08360428287608</t>
+        </is>
+      </c>
+      <c r="V392" t="inlineStr">
+        <is>
+          <t>-36.7874527358573,175.08450035356552</t>
+        </is>
+      </c>
+      <c r="W392" t="inlineStr">
+        <is>
+          <t>-36.787508828571234,175.08540496091442</t>
+        </is>
+      </c>
+      <c r="X392" t="inlineStr">
+        <is>
+          <t>-36.78758228385353,175.0863067216159</t>
+        </is>
+      </c>
+      <c r="Y392" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>-36.78510460998004,175.0668882754837</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>-36.78532304118208,175.0677452374448</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>-36.78551795775271,175.068609965116</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>-36.785739789680825,175.06946484642296</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>-36.78591771478317,175.07033403798337</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>-36.786091162618064,175.07120525886953</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>-36.7862366332422,175.07208474177264</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>-36.786339608706434,175.07295640275575</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>-36.78646813485936,175.0738166046568</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>-36.786628556286026,175.0747016737168</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>-36.786755836355006,175.0755929008958</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>-36.78685014932921,175.07648549335676</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>-36.78691515073839,175.07737550139896</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>-36.787019034030735,175.07824714143723</t>
+        </is>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>-36.78708868647613,175.07913256325642</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>-36.78715915690292,175.0800267478514</t>
+        </is>
+      </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>-36.7872256997121,175.08091957724616</t>
+        </is>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>-36.78728923618505,175.0818123098209</t>
+        </is>
+      </c>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>-36.78732596308162,175.08270881004165</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>-36.78738780317348,175.08360406195035</t>
+        </is>
+      </c>
+      <c r="V393" t="inlineStr">
+        <is>
+          <t>-36.78745093719111,175.08450049345842</t>
+        </is>
+      </c>
+      <c r="W393" t="inlineStr">
+        <is>
+          <t>-36.78750757271643,175.0854051094809</t>
+        </is>
+      </c>
+      <c r="X393" t="inlineStr">
+        <is>
+          <t>-36.787588991141696,175.0863056924252</t>
+        </is>
+      </c>
+      <c r="Y393" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>-36.78509154656816,175.0668925897601</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>-36.785308148874854,175.06775015562263</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>-36.78550898752176,175.0686129274672</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>-36.78572627211876,175.06946921599413</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>-36.78591046510764,175.07033632339358</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>-36.78608819105189,175.0712061860905</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>-36.78623155935818,175.07208629981827</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>-36.7863428880872,175.07295565517077</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>-36.78646831395487,175.073816579677</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>-36.78662623279671,175.07470204737373</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>-36.78675325803735,175.07559342976882</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>-36.78685068213626,175.07648537923245</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>-36.7869138140219,175.07737575043072</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>-36.78701571663539,175.07824755518584</t>
+        </is>
+      </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>-36.78708572081928,175.07913283342094</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>-36.78715466348314,175.0800271571576</t>
+        </is>
+      </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>-36.78722300259396,175.08091980399305</t>
+        </is>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>-36.78727799278318,175.0818131491512</t>
+        </is>
+      </c>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>-36.78731561797469,175.08270955736901</t>
+        </is>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>-36.78737970700299,175.08360464675377</t>
+        </is>
+      </c>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>-36.78744005526077,175.08450133981026</t>
+        </is>
+      </c>
+      <c r="W394" t="inlineStr">
+        <is>
+          <t>-36.78749384801746,175.08540673310003</t>
+        </is>
+      </c>
+      <c r="X394" t="inlineStr">
+        <is>
+          <t>-36.78757870663317,175.08630727051752</t>
+        </is>
+      </c>
+      <c r="Y394" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
